--- a/research/traditional_assets/database/data/malta/malta_transportation.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_transportation.xlsx
@@ -1191,7 +1191,7 @@
         <v>0.0929556750534281</v>
       </c>
       <c r="X2">
-        <v>0.130743110529236</v>
+        <v>0.130743110529237</v>
       </c>
       <c r="Y2">
         <v>0.8636727489925859</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09056299425631031</v>
+        <v>0.09027527377641324</v>
       </c>
       <c r="C2">
-        <v>41.85789065007124</v>
+        <v>41.5201512251469</v>
       </c>
       <c r="D2">
-        <v>36.22789065007124</v>
+        <v>36.31330478300341</v>
       </c>
       <c r="E2">
-        <v>-3.215355785650881</v>
+        <v>-2.792202227794373</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4231535578565088</v>
       </c>
       <c r="G2">
         <v>5.63</v>
@@ -1451,28 +1451,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02128462396018239</v>
       </c>
       <c r="N2">
-        <v>4.749000000000001</v>
+        <v>4.727715376039818</v>
       </c>
       <c r="O2">
-        <v>1.66215</v>
+        <v>1.654700381613936</v>
       </c>
       <c r="P2">
-        <v>3.086850000000001</v>
+        <v>3.073014994425882</v>
       </c>
       <c r="Q2">
-        <v>5.86685</v>
+        <v>5.853014994425882</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09056299425631031</v>
+        <v>0.09085689270344771</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8252328131907787</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>223.1188114426667</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09027527377641324</v>
+        <v>0.08998755329651614</v>
       </c>
       <c r="C3">
-        <v>41.5201512251469</v>
+        <v>41.18281551213208</v>
       </c>
       <c r="D3">
-        <v>36.31330478300341</v>
+        <v>36.3991226278451</v>
       </c>
       <c r="E3">
-        <v>-2.792202227794373</v>
+        <v>-2.369048669937864</v>
       </c>
       <c r="F3">
-        <v>0.4231535578565088</v>
+        <v>0.8463071157130176</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -1533,28 +1533,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M3">
-        <v>0.02128462396018239</v>
+        <v>0.04256924792036478</v>
       </c>
       <c r="N3">
-        <v>4.727715376039818</v>
+        <v>4.706430752079636</v>
       </c>
       <c r="O3">
-        <v>1.654700381613936</v>
+        <v>1.647250763227873</v>
       </c>
       <c r="P3">
-        <v>3.073014994425882</v>
+        <v>3.059179988851763</v>
       </c>
       <c r="Q3">
-        <v>5.853014994425882</v>
+        <v>5.839179988851763</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09085689270344771</v>
+        <v>0.0911567890780777</v>
       </c>
       <c r="T3">
-        <v>0.8252328131907787</v>
+        <v>0.8307255206113835</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>223.1188114426667</v>
+        <v>111.5594057213333</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08998755329651614</v>
+        <v>0.08969983281661906</v>
       </c>
       <c r="C4">
-        <v>41.18281551213208</v>
+        <v>40.84588638003775</v>
       </c>
       <c r="D4">
-        <v>36.3991226278451</v>
+        <v>36.48534705360728</v>
       </c>
       <c r="E4">
-        <v>-2.369048669937864</v>
+        <v>-1.945895112081355</v>
       </c>
       <c r="F4">
-        <v>0.8463071157130176</v>
+        <v>1.269460673569526</v>
       </c>
       <c r="G4">
         <v>5.63</v>
@@ -1615,28 +1615,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M4">
-        <v>0.04256924792036478</v>
+        <v>0.06385387188054717</v>
       </c>
       <c r="N4">
-        <v>4.706430752079636</v>
+        <v>4.685146128119453</v>
       </c>
       <c r="O4">
-        <v>1.647250763227873</v>
+        <v>1.639801144841809</v>
       </c>
       <c r="P4">
-        <v>3.059179988851763</v>
+        <v>3.045344983277645</v>
       </c>
       <c r="Q4">
-        <v>5.839179988851763</v>
+        <v>5.825344983277644</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0911567890780777</v>
+        <v>0.09146286888311243</v>
       </c>
       <c r="T4">
-        <v>0.8307255206113835</v>
+        <v>0.8363314797313821</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>111.5594057213333</v>
+        <v>74.37293714755556</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08969983281661906</v>
+        <v>0.08941211233672197</v>
       </c>
       <c r="C5">
-        <v>40.84588638003775</v>
+        <v>40.5093667251246</v>
       </c>
       <c r="D5">
-        <v>36.48534705360728</v>
+        <v>36.57198095655063</v>
       </c>
       <c r="E5">
-        <v>-1.945895112081355</v>
+        <v>-1.522741554224846</v>
       </c>
       <c r="F5">
-        <v>1.269460673569526</v>
+        <v>1.692614231426035</v>
       </c>
       <c r="G5">
         <v>5.63</v>
@@ -1697,28 +1697,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M5">
-        <v>0.06385387188054717</v>
+        <v>0.08513849584072956</v>
       </c>
       <c r="N5">
-        <v>4.685146128119453</v>
+        <v>4.663861504159271</v>
       </c>
       <c r="O5">
-        <v>1.639801144841809</v>
+        <v>1.632351526455745</v>
       </c>
       <c r="P5">
-        <v>3.045344983277645</v>
+        <v>3.031509977703526</v>
       </c>
       <c r="Q5">
-        <v>5.825344983277644</v>
+        <v>5.811509977703526</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09146286888311243</v>
+        <v>0.09177532535075206</v>
       </c>
       <c r="T5">
-        <v>0.8363314797313821</v>
+        <v>0.8420542296663809</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.37293714755556</v>
+        <v>55.77970286066667</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08941211233672197</v>
+        <v>0.0891243918568249</v>
       </c>
       <c r="C6">
-        <v>40.5093667251246</v>
+        <v>40.17325947122727</v>
       </c>
       <c r="D6">
-        <v>36.57198095655063</v>
+        <v>36.65902726050981</v>
       </c>
       <c r="E6">
-        <v>-1.522741554224846</v>
+        <v>-1.099587996368337</v>
       </c>
       <c r="F6">
-        <v>1.692614231426035</v>
+        <v>2.115767789282544</v>
       </c>
       <c r="G6">
         <v>5.63</v>
@@ -1779,28 +1779,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M6">
-        <v>0.08513849584072956</v>
+        <v>0.106423119800912</v>
       </c>
       <c r="N6">
-        <v>4.663861504159271</v>
+        <v>4.642576880199089</v>
       </c>
       <c r="O6">
-        <v>1.632351526455745</v>
+        <v>1.624901908069681</v>
       </c>
       <c r="P6">
-        <v>3.031509977703526</v>
+        <v>3.017674972129408</v>
       </c>
       <c r="Q6">
-        <v>5.811509977703526</v>
+        <v>5.797674972129407</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09177532535075206</v>
+        <v>0.09209435984928936</v>
       </c>
       <c r="T6">
-        <v>0.8420542296663809</v>
+        <v>0.8478974585473796</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.77970286066667</v>
+        <v>44.62376228853334</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0891243918568249</v>
+        <v>0.0888366713769278</v>
       </c>
       <c r="C7">
-        <v>40.17325947122727</v>
+        <v>39.83756757008337</v>
       </c>
       <c r="D7">
-        <v>36.65902726050981</v>
+        <v>36.74648891722241</v>
       </c>
       <c r="E7">
-        <v>-1.099587996368337</v>
+        <v>-0.6764344385118286</v>
       </c>
       <c r="F7">
-        <v>2.115767789282544</v>
+        <v>2.538921347139053</v>
       </c>
       <c r="G7">
         <v>5.63</v>
@@ -1861,28 +1861,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M7">
-        <v>0.106423119800912</v>
+        <v>0.1277077437610943</v>
       </c>
       <c r="N7">
-        <v>4.642576880199089</v>
+        <v>4.621292256238906</v>
       </c>
       <c r="O7">
-        <v>1.624901908069681</v>
+        <v>1.617452289683617</v>
       </c>
       <c r="P7">
-        <v>3.017674972129408</v>
+        <v>3.003839966555289</v>
       </c>
       <c r="Q7">
-        <v>5.797674972129407</v>
+        <v>5.78383996655529</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09209435984928936</v>
+        <v>0.09242018231588064</v>
       </c>
       <c r="T7">
-        <v>0.8478974585473796</v>
+        <v>0.853865011447123</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.62376228853334</v>
+        <v>37.18646857377778</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0888366713769278</v>
+        <v>0.08854895089703071</v>
       </c>
       <c r="C8">
-        <v>39.83756757008337</v>
+        <v>39.502294001667</v>
       </c>
       <c r="D8">
-        <v>36.74648891722241</v>
+        <v>36.83436890666256</v>
       </c>
       <c r="E8">
-        <v>-0.6764344385118286</v>
+        <v>-0.25328088065532</v>
       </c>
       <c r="F8">
-        <v>2.538921347139053</v>
+        <v>2.962074904995561</v>
       </c>
       <c r="G8">
         <v>5.63</v>
@@ -1943,28 +1943,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1277077437610943</v>
+        <v>0.1489923677212767</v>
       </c>
       <c r="N8">
-        <v>4.621292256238906</v>
+        <v>4.600007632278724</v>
       </c>
       <c r="O8">
-        <v>1.617452289683617</v>
+        <v>1.610002671297553</v>
       </c>
       <c r="P8">
-        <v>3.003839966555289</v>
+        <v>2.990004960981171</v>
       </c>
       <c r="Q8">
-        <v>5.78383996655529</v>
+        <v>5.77000496098117</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09242018231588064</v>
+        <v>0.09275301171723732</v>
       </c>
       <c r="T8">
-        <v>0.853865011447123</v>
+        <v>0.8599608988178284</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.18646857377778</v>
+        <v>31.87411592038096</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0885489508970307</v>
+        <v>0.08826123041713363</v>
       </c>
       <c r="C9">
-        <v>39.502294001667</v>
+        <v>39.16744177452735</v>
       </c>
       <c r="D9">
-        <v>36.83436890666256</v>
+        <v>36.92267023737942</v>
       </c>
       <c r="E9">
-        <v>-0.2532808806553195</v>
+        <v>0.1698726772011891</v>
       </c>
       <c r="F9">
-        <v>2.962074904995562</v>
+        <v>3.385228462852071</v>
       </c>
       <c r="G9">
         <v>5.63</v>
@@ -2025,28 +2025,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1489923677212767</v>
+        <v>0.1702769916814591</v>
       </c>
       <c r="N9">
-        <v>4.600007632278724</v>
+        <v>4.578723008318542</v>
       </c>
       <c r="O9">
-        <v>1.610002671297553</v>
+        <v>1.60255305291149</v>
       </c>
       <c r="P9">
-        <v>2.990004960981171</v>
+        <v>2.976169955407052</v>
       </c>
       <c r="Q9">
-        <v>5.77000496098117</v>
+        <v>5.756169955407051</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09275301171723732</v>
+        <v>0.09309307654036264</v>
       </c>
       <c r="T9">
-        <v>0.8599608988178284</v>
+        <v>0.8661893054792015</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.87411592038096</v>
+        <v>27.88985143033334</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08826123041713363</v>
+        <v>0.08797350993723656</v>
       </c>
       <c r="C10">
-        <v>39.16744177452735</v>
+        <v>38.83301392613191</v>
       </c>
       <c r="D10">
-        <v>36.92267023737942</v>
+        <v>37.01139594684049</v>
       </c>
       <c r="E10">
-        <v>0.1698726772011891</v>
+        <v>0.5930262350576978</v>
       </c>
       <c r="F10">
-        <v>3.385228462852071</v>
+        <v>3.808382020708579</v>
       </c>
       <c r="G10">
         <v>5.63</v>
@@ -2107,28 +2107,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M10">
-        <v>0.1702769916814591</v>
+        <v>0.1915616156416415</v>
       </c>
       <c r="N10">
-        <v>4.578723008318542</v>
+        <v>4.557438384358359</v>
       </c>
       <c r="O10">
-        <v>1.60255305291149</v>
+        <v>1.595103434525426</v>
       </c>
       <c r="P10">
-        <v>2.976169955407052</v>
+        <v>2.962334949832933</v>
       </c>
       <c r="Q10">
-        <v>5.756169955407051</v>
+        <v>5.742334949832934</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09309307654036264</v>
+        <v>0.09344061531564456</v>
       </c>
       <c r="T10">
-        <v>0.8661893054792015</v>
+        <v>0.8725546001990664</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.88985143033334</v>
+        <v>24.79097904918519</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08797350993723656</v>
+        <v>0.08768578945733946</v>
       </c>
       <c r="C11">
-        <v>38.83301392613191</v>
+        <v>38.49901352321483</v>
       </c>
       <c r="D11">
-        <v>37.01139594684049</v>
+        <v>37.10054910177992</v>
       </c>
       <c r="E11">
-        <v>0.5930262350576978</v>
+        <v>1.016179792914206</v>
       </c>
       <c r="F11">
-        <v>3.808382020708579</v>
+        <v>4.231535578565087</v>
       </c>
       <c r="G11">
         <v>5.63</v>
@@ -2189,28 +2189,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M11">
-        <v>0.1915616156416415</v>
+        <v>0.2128462396018239</v>
       </c>
       <c r="N11">
-        <v>4.557438384358359</v>
+        <v>4.536153760398177</v>
       </c>
       <c r="O11">
-        <v>1.595103434525426</v>
+        <v>1.587653816139362</v>
       </c>
       <c r="P11">
-        <v>2.962334949832933</v>
+        <v>2.948499944258815</v>
       </c>
       <c r="Q11">
-        <v>5.742334949832934</v>
+        <v>5.728499944258814</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09344061531564456</v>
+        <v>0.09379587717482163</v>
       </c>
       <c r="T11">
-        <v>0.8725546001990664</v>
+        <v>0.8790613459127059</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.79097904918519</v>
+        <v>22.31188114426667</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08768578945733946</v>
+        <v>0.08739806897744237</v>
       </c>
       <c r="C12">
-        <v>38.49901352321483</v>
+        <v>38.16544366213025</v>
       </c>
       <c r="D12">
-        <v>37.10054910177992</v>
+        <v>37.19013279855184</v>
       </c>
       <c r="E12">
-        <v>1.016179792914207</v>
+        <v>1.439333350770716</v>
       </c>
       <c r="F12">
-        <v>4.231535578565088</v>
+        <v>4.654689136421597</v>
       </c>
       <c r="G12">
         <v>5.63</v>
@@ -2271,28 +2271,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M12">
-        <v>0.2128462396018239</v>
+        <v>0.2341308635620063</v>
       </c>
       <c r="N12">
-        <v>4.536153760398177</v>
+        <v>4.514869136437994</v>
       </c>
       <c r="O12">
-        <v>1.587653816139362</v>
+        <v>1.580204197753298</v>
       </c>
       <c r="P12">
-        <v>2.948499944258815</v>
+        <v>2.934664938684696</v>
       </c>
       <c r="Q12">
-        <v>5.728499944258814</v>
+        <v>5.714664938684696</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09379587717482163</v>
+        <v>0.09415912244656446</v>
       </c>
       <c r="T12">
-        <v>0.8790613459127059</v>
+        <v>0.8857143106311465</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.31188114426667</v>
+        <v>20.2835283129697</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08739806897744237</v>
+        <v>0.08711034849754529</v>
       </c>
       <c r="C13">
-        <v>38.16544366213025</v>
+        <v>37.83230746921075</v>
       </c>
       <c r="D13">
-        <v>37.19013279855184</v>
+        <v>37.28015016348885</v>
       </c>
       <c r="E13">
-        <v>1.439333350770716</v>
+        <v>1.862486908627224</v>
       </c>
       <c r="F13">
-        <v>4.654689136421597</v>
+        <v>5.077842694278106</v>
       </c>
       <c r="G13">
         <v>5.63</v>
@@ -2353,28 +2353,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M13">
-        <v>0.2341308635620063</v>
+        <v>0.2554154875221887</v>
       </c>
       <c r="N13">
-        <v>4.514869136437994</v>
+        <v>4.493584512477812</v>
       </c>
       <c r="O13">
-        <v>1.580204197753298</v>
+        <v>1.572754579367234</v>
       </c>
       <c r="P13">
-        <v>2.934664938684696</v>
+        <v>2.920829933110578</v>
       </c>
       <c r="Q13">
-        <v>5.714664938684696</v>
+        <v>5.700829933110578</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09415912244656446</v>
+        <v>0.09453062329266509</v>
       </c>
       <c r="T13">
-        <v>0.8857143106311465</v>
+        <v>0.8925184790931878</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.2835283129697</v>
+        <v>18.59323428688889</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08711034849754529</v>
+        <v>0.0868226280176482</v>
       </c>
       <c r="C14">
-        <v>37.83230746921075</v>
+        <v>37.49960810113102</v>
       </c>
       <c r="D14">
-        <v>37.28015016348885</v>
+        <v>37.37060435326563</v>
       </c>
       <c r="E14">
-        <v>1.862486908627224</v>
+        <v>2.285640466483733</v>
       </c>
       <c r="F14">
-        <v>5.077842694278106</v>
+        <v>5.500996252134614</v>
       </c>
       <c r="G14">
         <v>5.63</v>
@@ -2435,28 +2435,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M14">
-        <v>0.2554154875221887</v>
+        <v>0.2767001114823711</v>
       </c>
       <c r="N14">
-        <v>4.493584512477812</v>
+        <v>4.47229988851763</v>
       </c>
       <c r="O14">
-        <v>1.572754579367234</v>
+        <v>1.56530496098117</v>
       </c>
       <c r="P14">
-        <v>2.920829933110578</v>
+        <v>2.906994927536459</v>
       </c>
       <c r="Q14">
-        <v>5.700829933110578</v>
+        <v>5.686994927536459</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09453062329266509</v>
+        <v>0.09491066438810138</v>
       </c>
       <c r="T14">
-        <v>0.8925184790931878</v>
+        <v>0.8994790652210232</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.59323428688889</v>
+        <v>17.16298549558975</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0868226280176482</v>
+        <v>0.08653490753775113</v>
       </c>
       <c r="C15">
-        <v>37.49960810113102</v>
+        <v>37.16734874527693</v>
       </c>
       <c r="D15">
-        <v>37.37060435326563</v>
+        <v>37.46149855526804</v>
       </c>
       <c r="E15">
-        <v>2.285640466483733</v>
+        <v>2.708794024340242</v>
       </c>
       <c r="F15">
-        <v>5.500996252134614</v>
+        <v>5.924149809991124</v>
       </c>
       <c r="G15">
         <v>5.63</v>
@@ -2517,28 +2517,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M15">
-        <v>0.2767001114823711</v>
+        <v>0.2979847354425535</v>
       </c>
       <c r="N15">
-        <v>4.47229988851763</v>
+        <v>4.451015264557447</v>
       </c>
       <c r="O15">
-        <v>1.56530496098117</v>
+        <v>1.557855342595106</v>
       </c>
       <c r="P15">
-        <v>2.906994927536459</v>
+        <v>2.893159921962341</v>
       </c>
       <c r="Q15">
-        <v>5.686994927536459</v>
+        <v>5.673159921962341</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09491066438810138</v>
+        <v>0.09529954364854781</v>
       </c>
       <c r="T15">
-        <v>0.8994790652210232</v>
+        <v>0.9066015254448549</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.16298549558975</v>
+        <v>15.93705796019048</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08653490753775113</v>
+        <v>0.08624718705785403</v>
       </c>
       <c r="C16">
-        <v>37.16734874527693</v>
+        <v>36.83553262011988</v>
       </c>
       <c r="D16">
-        <v>37.46149855526804</v>
+        <v>37.55283598796751</v>
       </c>
       <c r="E16">
-        <v>2.708794024340242</v>
+        <v>3.131947582196751</v>
       </c>
       <c r="F16">
-        <v>5.924149809991124</v>
+        <v>6.347303367847632</v>
       </c>
       <c r="G16">
         <v>5.63</v>
@@ -2599,28 +2599,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M16">
-        <v>0.2979847354425535</v>
+        <v>0.3192693594027359</v>
       </c>
       <c r="N16">
-        <v>4.451015264557447</v>
+        <v>4.429730640597264</v>
       </c>
       <c r="O16">
-        <v>1.557855342595106</v>
+        <v>1.550405724209042</v>
       </c>
       <c r="P16">
-        <v>2.893159921962341</v>
+        <v>2.879324916388222</v>
       </c>
       <c r="Q16">
-        <v>5.673159921962341</v>
+        <v>5.659324916388222</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09529954364854781</v>
+        <v>0.09569757300924003</v>
       </c>
       <c r="T16">
-        <v>0.9066015254448549</v>
+        <v>0.9138915729680708</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.93705796019048</v>
+        <v>14.87458742951111</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08624718705785403</v>
+        <v>0.08595946657795694</v>
       </c>
       <c r="C17">
-        <v>36.83553262011988</v>
+        <v>36.50416297559665</v>
       </c>
       <c r="D17">
-        <v>37.55283598796751</v>
+        <v>37.64461990130079</v>
       </c>
       <c r="E17">
-        <v>3.13194758219675</v>
+        <v>3.55510114005326</v>
       </c>
       <c r="F17">
-        <v>6.347303367847632</v>
+        <v>6.770456925704141</v>
       </c>
       <c r="G17">
         <v>5.63</v>
@@ -2681,28 +2681,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M17">
-        <v>0.3192693594027359</v>
+        <v>0.3405539833629183</v>
       </c>
       <c r="N17">
-        <v>4.429730640597264</v>
+        <v>4.408446016637082</v>
       </c>
       <c r="O17">
-        <v>1.550405724209042</v>
+        <v>1.542956105822979</v>
       </c>
       <c r="P17">
-        <v>2.879324916388222</v>
+        <v>2.865489910814103</v>
       </c>
       <c r="Q17">
-        <v>5.659324916388222</v>
+        <v>5.645489910814103</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09569757300924003</v>
+        <v>0.09610507925947255</v>
       </c>
       <c r="T17">
-        <v>0.9138915729680708</v>
+        <v>0.9213551930513632</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.87458742951111</v>
+        <v>13.94492571516667</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08595946657795694</v>
+        <v>0.08567174609805986</v>
       </c>
       <c r="C18">
-        <v>36.50416297559665</v>
+        <v>36.17324309349493</v>
       </c>
       <c r="D18">
-        <v>37.64461990130079</v>
+        <v>37.73685357705558</v>
       </c>
       <c r="E18">
-        <v>3.55510114005326</v>
+        <v>3.978254697909768</v>
       </c>
       <c r="F18">
-        <v>6.770456925704141</v>
+        <v>7.19361048356065</v>
       </c>
       <c r="G18">
         <v>5.63</v>
@@ -2763,28 +2763,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M18">
-        <v>0.3405539833629183</v>
+        <v>0.3618386073231007</v>
       </c>
       <c r="N18">
-        <v>4.408446016637082</v>
+        <v>4.3871613926769</v>
       </c>
       <c r="O18">
-        <v>1.542956105822979</v>
+        <v>1.535506487436915</v>
       </c>
       <c r="P18">
-        <v>2.865489910814103</v>
+        <v>2.851654905239985</v>
       </c>
       <c r="Q18">
-        <v>5.645489910814103</v>
+        <v>5.631654905239985</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09610507925947255</v>
+        <v>0.09652240493742152</v>
       </c>
       <c r="T18">
-        <v>0.9213551930513632</v>
+        <v>0.928998659401723</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.94492571516667</v>
+        <v>13.12463596721569</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08567174609805986</v>
+        <v>0.08555952561816277</v>
       </c>
       <c r="C19">
-        <v>36.17324309349493</v>
+        <v>35.78618634818861</v>
       </c>
       <c r="D19">
-        <v>37.73685357705558</v>
+        <v>37.77295038960577</v>
       </c>
       <c r="E19">
-        <v>3.978254697909768</v>
+        <v>4.401408255766277</v>
       </c>
       <c r="F19">
-        <v>7.19361048356065</v>
+        <v>7.616764041417159</v>
       </c>
       <c r="G19">
         <v>5.63</v>
@@ -2845,45 +2845,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M19">
-        <v>0.3618386073231007</v>
+        <v>0.3945483773454088</v>
       </c>
       <c r="N19">
-        <v>4.3871613926769</v>
+        <v>4.354451622654592</v>
       </c>
       <c r="O19">
-        <v>1.535506487436915</v>
+        <v>1.524058067929107</v>
       </c>
       <c r="P19">
-        <v>2.851654905239985</v>
+        <v>2.830393554725485</v>
       </c>
       <c r="Q19">
-        <v>5.631654905239985</v>
+        <v>5.610393554725485</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09652240493742152</v>
+        <v>0.09694990929044241</v>
       </c>
       <c r="T19">
-        <v>0.928998659401723</v>
+        <v>0.936828551760628</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.12463596721569</v>
+        <v>12.03654677774146</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08555952561816278</v>
+        <v>0.0852815551382657</v>
       </c>
       <c r="C20">
-        <v>35.78618634818861</v>
+        <v>35.45274278869616</v>
       </c>
       <c r="D20">
-        <v>37.77295038960576</v>
+        <v>37.86266038796982</v>
       </c>
       <c r="E20">
-        <v>4.401408255766277</v>
+        <v>4.824561813622786</v>
       </c>
       <c r="F20">
-        <v>7.616764041417158</v>
+        <v>8.039917599273668</v>
       </c>
       <c r="G20">
         <v>5.63</v>
@@ -2927,28 +2927,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M20">
-        <v>0.3945483773454088</v>
+        <v>0.416467731642376</v>
       </c>
       <c r="N20">
-        <v>4.354451622654592</v>
+        <v>4.332532268357625</v>
       </c>
       <c r="O20">
-        <v>1.524058067929107</v>
+        <v>1.516386293925168</v>
       </c>
       <c r="P20">
-        <v>2.830393554725485</v>
+        <v>2.816145974432456</v>
       </c>
       <c r="Q20">
-        <v>5.610393554725485</v>
+        <v>5.596145974432456</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09694990929044241</v>
+        <v>0.09738796930650086</v>
       </c>
       <c r="T20">
-        <v>0.936828551760628</v>
+        <v>0.9448517747950618</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.03654677774146</v>
+        <v>11.40304431575506</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0852815551382657</v>
+        <v>0.08500358465836862</v>
       </c>
       <c r="C21">
-        <v>35.45274278869616</v>
+        <v>35.11972636252466</v>
       </c>
       <c r="D21">
-        <v>37.86266038796982</v>
+        <v>37.95279751965484</v>
       </c>
       <c r="E21">
-        <v>4.824561813622786</v>
+        <v>5.247715371479295</v>
       </c>
       <c r="F21">
-        <v>8.039917599273668</v>
+        <v>8.463071157130177</v>
       </c>
       <c r="G21">
         <v>5.63</v>
@@ -3009,28 +3009,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M21">
-        <v>0.416467731642376</v>
+        <v>0.4383870859393432</v>
       </c>
       <c r="N21">
-        <v>4.332532268357625</v>
+        <v>4.310612914060657</v>
       </c>
       <c r="O21">
-        <v>1.516386293925168</v>
+        <v>1.50871451992123</v>
       </c>
       <c r="P21">
-        <v>2.816145974432456</v>
+        <v>2.801898394139427</v>
       </c>
       <c r="Q21">
-        <v>5.596145974432456</v>
+        <v>5.581898394139428</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09738796930650086</v>
+        <v>0.09783698082296076</v>
       </c>
       <c r="T21">
-        <v>0.9448517747950618</v>
+        <v>0.9530755784053562</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.40304431575506</v>
+        <v>10.83289209996731</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08500358465836862</v>
+        <v>0.08472561417847152</v>
       </c>
       <c r="C22">
-        <v>35.11972636252466</v>
+        <v>34.78714012749785</v>
       </c>
       <c r="D22">
-        <v>37.95279751965484</v>
+        <v>38.04336484248454</v>
       </c>
       <c r="E22">
-        <v>5.247715371479295</v>
+        <v>5.670868929335803</v>
       </c>
       <c r="F22">
-        <v>8.463071157130177</v>
+        <v>8.886224714986685</v>
       </c>
       <c r="G22">
         <v>5.63</v>
@@ -3091,28 +3091,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M22">
-        <v>0.4383870859393432</v>
+        <v>0.4603064402363103</v>
       </c>
       <c r="N22">
-        <v>4.310612914060657</v>
+        <v>4.28869355976369</v>
       </c>
       <c r="O22">
-        <v>1.50871451992123</v>
+        <v>1.501042745917291</v>
       </c>
       <c r="P22">
-        <v>2.801898394139427</v>
+        <v>2.787650813846398</v>
       </c>
       <c r="Q22">
-        <v>5.581898394139428</v>
+        <v>5.567650813846399</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09783698082296076</v>
+        <v>0.0982973597195842</v>
       </c>
       <c r="T22">
-        <v>0.9530755784053562</v>
+        <v>0.9615075795754049</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.83289209996731</v>
+        <v>10.31704009520696</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08472561417847152</v>
+        <v>0.08444764369857444</v>
       </c>
       <c r="C23">
-        <v>34.78714012749786</v>
+        <v>34.45498717069695</v>
       </c>
       <c r="D23">
-        <v>38.04336484248454</v>
+        <v>38.13436544354015</v>
       </c>
       <c r="E23">
-        <v>5.670868929335802</v>
+        <v>6.094022487192312</v>
       </c>
       <c r="F23">
-        <v>8.886224714986684</v>
+        <v>9.309378272843194</v>
       </c>
       <c r="G23">
         <v>5.63</v>
@@ -3173,28 +3173,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M23">
-        <v>0.4603064402363102</v>
+        <v>0.4822257945332775</v>
       </c>
       <c r="N23">
-        <v>4.28869355976369</v>
+        <v>4.266774205466723</v>
       </c>
       <c r="O23">
-        <v>1.501042745917291</v>
+        <v>1.493370971913353</v>
       </c>
       <c r="P23">
-        <v>2.787650813846398</v>
+        <v>2.77340323355337</v>
       </c>
       <c r="Q23">
-        <v>5.567650813846399</v>
+        <v>5.55340323355337</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0982973597195842</v>
+        <v>0.09876954320330056</v>
       </c>
       <c r="T23">
-        <v>0.9615075795754049</v>
+        <v>0.97015578590366</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.31704009520696</v>
+        <v>9.84808372724301</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08444764369857444</v>
+        <v>0.08442382321867734</v>
       </c>
       <c r="C24">
-        <v>34.45498717069695</v>
+        <v>34.03965209995086</v>
       </c>
       <c r="D24">
-        <v>38.13436544354015</v>
+        <v>38.14218393065055</v>
       </c>
       <c r="E24">
-        <v>6.094022487192312</v>
+        <v>6.517176045048821</v>
       </c>
       <c r="F24">
-        <v>9.309378272843194</v>
+        <v>9.732531830699703</v>
       </c>
       <c r="G24">
         <v>5.63</v>
@@ -3255,45 +3255,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M24">
-        <v>0.4822257945332775</v>
+        <v>0.5206904529424341</v>
       </c>
       <c r="N24">
-        <v>4.266774205466723</v>
+        <v>4.228309547057567</v>
       </c>
       <c r="O24">
-        <v>1.493370971913353</v>
+        <v>1.479908341470148</v>
       </c>
       <c r="P24">
-        <v>2.77340323355337</v>
+        <v>2.748401205587419</v>
       </c>
       <c r="Q24">
-        <v>5.55340323355337</v>
+        <v>5.528401205587418</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09876954320330056</v>
+        <v>0.09925399119308745</v>
       </c>
       <c r="T24">
-        <v>0.97015578590366</v>
+        <v>0.9790286209677139</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.84808372724301</v>
+        <v>9.120582052471462</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08442382321867734</v>
+        <v>0.08415690273878026</v>
       </c>
       <c r="C25">
-        <v>34.03965209995086</v>
+        <v>33.70432837267921</v>
       </c>
       <c r="D25">
-        <v>38.14218393065055</v>
+        <v>38.23001376123543</v>
       </c>
       <c r="E25">
-        <v>6.517176045048821</v>
+        <v>6.940329602905329</v>
       </c>
       <c r="F25">
-        <v>9.732531830699703</v>
+        <v>10.15568538855621</v>
       </c>
       <c r="G25">
         <v>5.63</v>
@@ -3337,28 +3337,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M25">
-        <v>0.5206904529424341</v>
+        <v>0.5433291682877573</v>
       </c>
       <c r="N25">
-        <v>4.228309547057567</v>
+        <v>4.205670831712244</v>
       </c>
       <c r="O25">
-        <v>1.479908341470148</v>
+        <v>1.471984791099285</v>
       </c>
       <c r="P25">
-        <v>2.748401205587419</v>
+        <v>2.733686040612958</v>
       </c>
       <c r="Q25">
-        <v>5.528401205587418</v>
+        <v>5.513686040612958</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09925399119308745</v>
+        <v>0.09975118781418454</v>
       </c>
       <c r="T25">
-        <v>0.9790286209677139</v>
+        <v>0.9881349516913482</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.120582052471462</v>
+        <v>8.740557800285151</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08415690273878026</v>
+        <v>0.08388998225888317</v>
       </c>
       <c r="C26">
-        <v>33.70432837267921</v>
+        <v>33.36941006966575</v>
       </c>
       <c r="D26">
-        <v>38.23001376123543</v>
+        <v>38.31824901607846</v>
       </c>
       <c r="E26">
-        <v>6.940329602905329</v>
+        <v>7.363483160761838</v>
       </c>
       <c r="F26">
-        <v>10.15568538855621</v>
+        <v>10.57883894641272</v>
       </c>
       <c r="G26">
         <v>5.63</v>
@@ -3419,28 +3419,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M26">
-        <v>0.5433291682877573</v>
+        <v>0.5659678836330805</v>
       </c>
       <c r="N26">
-        <v>4.205670831712244</v>
+        <v>4.18303211636692</v>
       </c>
       <c r="O26">
-        <v>1.471984791099285</v>
+        <v>1.464061240728422</v>
       </c>
       <c r="P26">
-        <v>2.733686040612958</v>
+        <v>2.718970875638498</v>
       </c>
       <c r="Q26">
-        <v>5.513686040612958</v>
+        <v>5.498970875638499</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09975118781418454</v>
+        <v>0.1002616430118442</v>
       </c>
       <c r="T26">
-        <v>0.9881349516913482</v>
+        <v>0.9974841179009463</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.740557800285151</v>
+        <v>8.390935488273746</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08388998225888317</v>
+        <v>0.08362306177898607</v>
       </c>
       <c r="C27">
-        <v>33.36941006966575</v>
+        <v>33.03490000457417</v>
       </c>
       <c r="D27">
-        <v>38.31824901607846</v>
+        <v>38.4068925088434</v>
       </c>
       <c r="E27">
-        <v>7.363483160761838</v>
+        <v>7.786636718618347</v>
       </c>
       <c r="F27">
-        <v>10.57883894641272</v>
+        <v>11.00199250426923</v>
       </c>
       <c r="G27">
         <v>5.63</v>
@@ -3501,28 +3501,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M27">
-        <v>0.5659678836330805</v>
+        <v>0.5886065989784037</v>
       </c>
       <c r="N27">
-        <v>4.18303211636692</v>
+        <v>4.160393401021597</v>
       </c>
       <c r="O27">
-        <v>1.464061240728422</v>
+        <v>1.456137690357559</v>
       </c>
       <c r="P27">
-        <v>2.718970875638498</v>
+        <v>2.704255710664039</v>
       </c>
       <c r="Q27">
-        <v>5.498970875638499</v>
+        <v>5.484255710664039</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1002616430118442</v>
+        <v>0.1007858942959271</v>
       </c>
       <c r="T27">
-        <v>0.9974841179009463</v>
+        <v>1.007085964278371</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.390935488273746</v>
+        <v>8.068207200263217</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08362306177898607</v>
+        <v>0.083356141299089</v>
       </c>
       <c r="C28">
-        <v>33.03490000457417</v>
+        <v>32.70080101716449</v>
       </c>
       <c r="D28">
-        <v>38.4068925088434</v>
+        <v>38.49594707929023</v>
       </c>
       <c r="E28">
-        <v>7.786636718618347</v>
+        <v>8.209790276474857</v>
       </c>
       <c r="F28">
-        <v>11.00199250426923</v>
+        <v>11.42514606212574</v>
       </c>
       <c r="G28">
         <v>5.63</v>
@@ -3583,28 +3583,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M28">
-        <v>0.5886065989784037</v>
+        <v>0.611245314323727</v>
       </c>
       <c r="N28">
-        <v>4.160393401021597</v>
+        <v>4.137754685676273</v>
       </c>
       <c r="O28">
-        <v>1.456137690357559</v>
+        <v>1.448214139986695</v>
       </c>
       <c r="P28">
-        <v>2.704255710664039</v>
+        <v>2.689540545689578</v>
       </c>
       <c r="Q28">
-        <v>5.484255710664039</v>
+        <v>5.469540545689577</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1007858942959271</v>
+        <v>0.101324508628889</v>
       </c>
       <c r="T28">
-        <v>1.007085964278371</v>
+        <v>1.016950874940109</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.068207200263217</v>
+        <v>7.769384711364578</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.083356141299089</v>
+        <v>0.08323482081919192</v>
       </c>
       <c r="C29">
-        <v>32.70080101716449</v>
+        <v>32.31826112770636</v>
       </c>
       <c r="D29">
-        <v>38.49594707929023</v>
+        <v>38.53656074768861</v>
       </c>
       <c r="E29">
-        <v>8.209790276474857</v>
+        <v>8.632943834331366</v>
       </c>
       <c r="F29">
-        <v>11.42514606212574</v>
+        <v>11.84829961998225</v>
       </c>
       <c r="G29">
         <v>5.63</v>
@@ -3665,45 +3665,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M29">
-        <v>0.611245314323727</v>
+        <v>0.6433626693650361</v>
       </c>
       <c r="N29">
-        <v>4.137754685676273</v>
+        <v>4.105637330634964</v>
       </c>
       <c r="O29">
-        <v>1.448214139986695</v>
+        <v>1.436973065722237</v>
       </c>
       <c r="P29">
-        <v>2.689540545689578</v>
+        <v>2.668664264912727</v>
       </c>
       <c r="Q29">
-        <v>5.469540545689577</v>
+        <v>5.448664264912727</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.101324508628889</v>
+        <v>0.1018780844710999</v>
       </c>
       <c r="T29">
-        <v>1.016950874940109</v>
+        <v>1.027089810898006</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.769384711364578</v>
+        <v>7.381528686902218</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08323482081919192</v>
+        <v>0.08297310033929482</v>
       </c>
       <c r="C30">
-        <v>32.31826112770636</v>
+        <v>31.98301453881546</v>
       </c>
       <c r="D30">
-        <v>38.53656074768861</v>
+        <v>38.62446771665422</v>
       </c>
       <c r="E30">
-        <v>8.632943834331366</v>
+        <v>9.056097392187874</v>
       </c>
       <c r="F30">
-        <v>11.84829961998225</v>
+        <v>12.27145317783876</v>
       </c>
       <c r="G30">
         <v>5.63</v>
@@ -3747,28 +3747,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M30">
-        <v>0.6433626693650361</v>
+        <v>0.6663399075566445</v>
       </c>
       <c r="N30">
-        <v>4.105637330634964</v>
+        <v>4.082660092443356</v>
       </c>
       <c r="O30">
-        <v>1.436973065722237</v>
+        <v>1.428931032355174</v>
       </c>
       <c r="P30">
-        <v>2.668664264912727</v>
+        <v>2.653729060088181</v>
       </c>
       <c r="Q30">
-        <v>5.448664264912727</v>
+        <v>5.433729060088181</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1018780844710999</v>
+        <v>0.1024472539990068</v>
       </c>
       <c r="T30">
-        <v>1.027089810898006</v>
+        <v>1.037514350685703</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.381528686902218</v>
+        <v>7.126993214940072</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08297310033929482</v>
+        <v>0.08271137985939774</v>
       </c>
       <c r="C31">
-        <v>31.98301453881546</v>
+        <v>31.64816992161581</v>
       </c>
       <c r="D31">
-        <v>38.62446771665422</v>
+        <v>38.71277665731107</v>
       </c>
       <c r="E31">
-        <v>9.056097392187873</v>
+        <v>9.479250950044381</v>
       </c>
       <c r="F31">
-        <v>12.27145317783875</v>
+        <v>12.69460673569526</v>
       </c>
       <c r="G31">
         <v>5.63</v>
@@ -3829,28 +3829,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M31">
-        <v>0.6663399075566444</v>
+        <v>0.6893171457482528</v>
       </c>
       <c r="N31">
-        <v>4.082660092443356</v>
+        <v>4.059682854251748</v>
       </c>
       <c r="O31">
-        <v>1.428931032355174</v>
+        <v>1.420888998988112</v>
       </c>
       <c r="P31">
-        <v>2.653729060088181</v>
+        <v>2.638793855263637</v>
       </c>
       <c r="Q31">
-        <v>5.433729060088181</v>
+        <v>5.418793855263637</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1024472539990068</v>
+        <v>0.1030326855134253</v>
       </c>
       <c r="T31">
-        <v>1.037514350685703</v>
+        <v>1.048236734467335</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.126993214940073</v>
+        <v>6.889426774442073</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08271137985939774</v>
+        <v>0.08244965937950066</v>
       </c>
       <c r="C32">
-        <v>31.64816992161581</v>
+        <v>31.31373003956608</v>
       </c>
       <c r="D32">
-        <v>38.71277665731107</v>
+        <v>38.80149033311785</v>
       </c>
       <c r="E32">
-        <v>9.479250950044381</v>
+        <v>9.90240450790089</v>
       </c>
       <c r="F32">
-        <v>12.69460673569526</v>
+        <v>13.11776029355177</v>
       </c>
       <c r="G32">
         <v>5.63</v>
@@ -3911,28 +3911,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M32">
-        <v>0.6893171457482528</v>
+        <v>0.7122943839398612</v>
       </c>
       <c r="N32">
-        <v>4.059682854251748</v>
+        <v>4.036705616060139</v>
       </c>
       <c r="O32">
-        <v>1.420888998988112</v>
+        <v>1.412846965621049</v>
       </c>
       <c r="P32">
-        <v>2.638793855263637</v>
+        <v>2.62385865043909</v>
       </c>
       <c r="Q32">
-        <v>5.418793855263637</v>
+        <v>5.403858650439091</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1030326855134253</v>
+        <v>0.1036350860572473</v>
       </c>
       <c r="T32">
-        <v>1.048236734467335</v>
+        <v>1.059269911981767</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.889426774442073</v>
+        <v>6.667187201072973</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08244965937950066</v>
+        <v>0.08218793889960356</v>
       </c>
       <c r="C33">
-        <v>31.31373003956608</v>
+        <v>30.97969768151396</v>
       </c>
       <c r="D33">
-        <v>38.80149033311785</v>
+        <v>38.89061153292224</v>
       </c>
       <c r="E33">
-        <v>9.90240450790089</v>
+        <v>10.3255580657574</v>
       </c>
       <c r="F33">
-        <v>13.11776029355177</v>
+        <v>13.54091385140828</v>
       </c>
       <c r="G33">
         <v>5.63</v>
@@ -3993,28 +3993,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M33">
-        <v>0.7122943839398612</v>
+        <v>0.7352716221314698</v>
       </c>
       <c r="N33">
-        <v>4.036705616060139</v>
+        <v>4.013728377868531</v>
       </c>
       <c r="O33">
-        <v>1.412846965621049</v>
+        <v>1.404804932253986</v>
       </c>
       <c r="P33">
-        <v>2.62385865043909</v>
+        <v>2.608923445614545</v>
       </c>
       <c r="Q33">
-        <v>5.403858650439091</v>
+        <v>5.388923445614545</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1036350860572473</v>
+        <v>0.1042552042641229</v>
       </c>
       <c r="T33">
-        <v>1.059269911981767</v>
+        <v>1.070627594717212</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.667187201072973</v>
+        <v>6.45883760103944</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08218793889960356</v>
+        <v>0.08192621841970647</v>
       </c>
       <c r="C34">
-        <v>30.97969768151396</v>
+        <v>30.64607566198839</v>
       </c>
       <c r="D34">
-        <v>38.89061153292224</v>
+        <v>38.98014307125318</v>
       </c>
       <c r="E34">
-        <v>10.3255580657574</v>
+        <v>10.74871162361391</v>
       </c>
       <c r="F34">
-        <v>13.54091385140828</v>
+        <v>13.96406740926479</v>
       </c>
       <c r="G34">
         <v>5.63</v>
@@ -4075,28 +4075,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M34">
-        <v>0.7352716221314698</v>
+        <v>0.7582488603230781</v>
       </c>
       <c r="N34">
-        <v>4.013728377868531</v>
+        <v>3.990751139676922</v>
       </c>
       <c r="O34">
-        <v>1.404804932253986</v>
+        <v>1.396762898886923</v>
       </c>
       <c r="P34">
-        <v>2.608923445614545</v>
+        <v>2.59398824079</v>
       </c>
       <c r="Q34">
-        <v>5.388923445614545</v>
+        <v>5.37398824079</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1042552042641229</v>
+        <v>0.1048938334622485</v>
       </c>
       <c r="T34">
-        <v>1.070627594717212</v>
+        <v>1.082324312758193</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.45883760103944</v>
+        <v>6.263115249492792</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08192621841970647</v>
+        <v>0.0818854979398094</v>
       </c>
       <c r="C35">
-        <v>30.64607566198839</v>
+        <v>30.2368891792245</v>
       </c>
       <c r="D35">
-        <v>38.98014307125318</v>
+        <v>38.9941101463458</v>
       </c>
       <c r="E35">
-        <v>10.74871162361391</v>
+        <v>11.17186518147042</v>
       </c>
       <c r="F35">
-        <v>13.96406740926479</v>
+        <v>14.3872209671213</v>
       </c>
       <c r="G35">
         <v>5.63</v>
@@ -4157,45 +4157,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M35">
-        <v>0.7582488603230781</v>
+        <v>0.7956133194818079</v>
       </c>
       <c r="N35">
-        <v>3.990751139676922</v>
+        <v>3.953386680518193</v>
       </c>
       <c r="O35">
-        <v>1.396762898886923</v>
+        <v>1.383685338181367</v>
       </c>
       <c r="P35">
-        <v>2.59398824079</v>
+        <v>2.569701342336825</v>
       </c>
       <c r="Q35">
-        <v>5.37398824079</v>
+        <v>5.349701342336825</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1048938334622485</v>
+        <v>0.1055518150603173</v>
       </c>
       <c r="T35">
-        <v>1.082324312758193</v>
+        <v>1.094375476800415</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.263115249492792</v>
+        <v>5.96898001040641</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0818854979398094</v>
+        <v>0.08163027745991232</v>
       </c>
       <c r="C36">
-        <v>30.2368891792245</v>
+        <v>29.90150441068454</v>
       </c>
       <c r="D36">
-        <v>38.9941101463458</v>
+        <v>39.08187893566235</v>
       </c>
       <c r="E36">
-        <v>11.17186518147042</v>
+        <v>11.59501873932693</v>
       </c>
       <c r="F36">
-        <v>14.3872209671213</v>
+        <v>14.81037452497781</v>
       </c>
       <c r="G36">
         <v>5.63</v>
@@ -4239,28 +4239,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M36">
-        <v>0.7956133194818079</v>
+        <v>0.819013711231273</v>
       </c>
       <c r="N36">
-        <v>3.953386680518193</v>
+        <v>3.929986288768728</v>
       </c>
       <c r="O36">
-        <v>1.383685338181367</v>
+        <v>1.375495201069055</v>
       </c>
       <c r="P36">
-        <v>2.569701342336825</v>
+        <v>2.554491087699673</v>
       </c>
       <c r="Q36">
-        <v>5.349701342336825</v>
+        <v>5.334491087699673</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1055518150603173</v>
+        <v>0.106230042246019</v>
       </c>
       <c r="T36">
-        <v>1.094375476800415</v>
+        <v>1.106797445890091</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.96898001040641</v>
+        <v>5.798437724394798</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08163027745991232</v>
+        <v>0.08137505698001521</v>
       </c>
       <c r="C37">
-        <v>29.90150441068454</v>
+        <v>29.56651563725023</v>
       </c>
       <c r="D37">
-        <v>39.08187893566235</v>
+        <v>39.17004372008455</v>
       </c>
       <c r="E37">
-        <v>11.59501873932693</v>
+        <v>12.01817229718344</v>
       </c>
       <c r="F37">
-        <v>14.81037452497781</v>
+        <v>15.23352808283432</v>
       </c>
       <c r="G37">
         <v>5.63</v>
@@ -4321,28 +4321,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M37">
-        <v>0.819013711231273</v>
+        <v>0.8424141029807378</v>
       </c>
       <c r="N37">
-        <v>3.929986288768728</v>
+        <v>3.906585897019263</v>
       </c>
       <c r="O37">
-        <v>1.375495201069055</v>
+        <v>1.367305063956742</v>
       </c>
       <c r="P37">
-        <v>2.554491087699673</v>
+        <v>2.539280833062521</v>
       </c>
       <c r="Q37">
-        <v>5.334491087699673</v>
+        <v>5.319280833062521</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.106230042246019</v>
+        <v>0.1069294640312738</v>
       </c>
       <c r="T37">
-        <v>1.106797445890091</v>
+        <v>1.119607601513819</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.798437724394798</v>
+        <v>5.637370009828276</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08137505698001522</v>
+        <v>0.08111983650011813</v>
       </c>
       <c r="C38">
-        <v>29.56651563725023</v>
+        <v>29.23192554495628</v>
       </c>
       <c r="D38">
-        <v>39.17004372008455</v>
+        <v>39.2586071856471</v>
       </c>
       <c r="E38">
-        <v>12.01817229718344</v>
+        <v>12.44132585503994</v>
       </c>
       <c r="F38">
-        <v>15.23352808283432</v>
+        <v>15.65668164069083</v>
       </c>
       <c r="G38">
         <v>5.63</v>
@@ -4403,28 +4403,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M38">
-        <v>0.8424141029807377</v>
+        <v>0.8658144947302027</v>
       </c>
       <c r="N38">
-        <v>3.906585897019263</v>
+        <v>3.883185505269798</v>
       </c>
       <c r="O38">
-        <v>1.367305063956742</v>
+        <v>1.359114926844429</v>
       </c>
       <c r="P38">
-        <v>2.539280833062521</v>
+        <v>2.524070578425369</v>
       </c>
       <c r="Q38">
-        <v>5.319280833062521</v>
+        <v>5.304070578425368</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1069294640312738</v>
+        <v>0.1076510896827272</v>
       </c>
       <c r="T38">
-        <v>1.119607601513819</v>
+        <v>1.132824428744649</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.637370009828278</v>
+        <v>5.485008658211296</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08111983650011813</v>
+        <v>0.08086461602022105</v>
       </c>
       <c r="C39">
-        <v>29.23192554495628</v>
+        <v>28.89773684418493</v>
       </c>
       <c r="D39">
-        <v>39.2586071856471</v>
+        <v>39.34757204273226</v>
       </c>
       <c r="E39">
-        <v>12.44132585503994</v>
+        <v>12.86447941289645</v>
       </c>
       <c r="F39">
-        <v>15.65668164069083</v>
+        <v>16.07983519854734</v>
       </c>
       <c r="G39">
         <v>5.63</v>
@@ -4485,28 +4485,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M39">
-        <v>0.8658144947302027</v>
+        <v>0.8892148864796677</v>
       </c>
       <c r="N39">
-        <v>3.883185505269798</v>
+        <v>3.859785113520333</v>
       </c>
       <c r="O39">
-        <v>1.359114926844429</v>
+        <v>1.350924789732116</v>
       </c>
       <c r="P39">
-        <v>2.524070578425369</v>
+        <v>2.508860323788216</v>
       </c>
       <c r="Q39">
-        <v>5.304070578425368</v>
+        <v>5.288860323788215</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1076510896827272</v>
+        <v>0.1083959935810017</v>
       </c>
       <c r="T39">
-        <v>1.132824428744649</v>
+        <v>1.14646760524099</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.485008658211296</v>
+        <v>5.340666325100472</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08086461602022105</v>
+        <v>0.08060939554032397</v>
       </c>
       <c r="C40">
-        <v>28.89773684418493</v>
+        <v>28.56395226994247</v>
       </c>
       <c r="D40">
-        <v>39.34757204273226</v>
+        <v>39.43694102634631</v>
       </c>
       <c r="E40">
-        <v>12.86447941289645</v>
+        <v>13.28763297075296</v>
       </c>
       <c r="F40">
-        <v>16.07983519854734</v>
+        <v>16.50298875640384</v>
       </c>
       <c r="G40">
         <v>5.63</v>
@@ -4567,28 +4567,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M40">
-        <v>0.8892148864796677</v>
+        <v>0.9126152782291327</v>
       </c>
       <c r="N40">
-        <v>3.859785113520333</v>
+        <v>3.836384721770868</v>
       </c>
       <c r="O40">
-        <v>1.350924789732116</v>
+        <v>1.342734652619804</v>
       </c>
       <c r="P40">
-        <v>2.508860323788216</v>
+        <v>2.493650069151064</v>
       </c>
       <c r="Q40">
-        <v>5.288860323788215</v>
+        <v>5.273650069151063</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1083959935810017</v>
+        <v>0.1091653205579081</v>
       </c>
       <c r="T40">
-        <v>1.14646760524099</v>
+        <v>1.160558098999507</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.340666325100472</v>
+        <v>5.203726162918408</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08060939554032397</v>
+        <v>0.08035417506042689</v>
       </c>
       <c r="C41">
-        <v>28.56395226994247</v>
+        <v>28.23057458213952</v>
       </c>
       <c r="D41">
-        <v>39.43694102634631</v>
+        <v>39.52671689639988</v>
       </c>
       <c r="E41">
-        <v>13.28763297075296</v>
+        <v>13.71078652860947</v>
       </c>
       <c r="F41">
-        <v>16.50298875640384</v>
+        <v>16.92614231426035</v>
       </c>
       <c r="G41">
         <v>5.63</v>
@@ -4649,28 +4649,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M41">
-        <v>0.9126152782291327</v>
+        <v>0.9360156699785975</v>
       </c>
       <c r="N41">
-        <v>3.836384721770868</v>
+        <v>3.812984330021403</v>
       </c>
       <c r="O41">
-        <v>1.342734652619804</v>
+        <v>1.334544515507491</v>
       </c>
       <c r="P41">
-        <v>2.493650069151064</v>
+        <v>2.478439814513912</v>
       </c>
       <c r="Q41">
-        <v>5.273650069151063</v>
+        <v>5.258439814513912</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1091653205579081</v>
+        <v>0.1099602917673781</v>
       </c>
       <c r="T41">
-        <v>1.160558098999507</v>
+        <v>1.175118275883307</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.203726162918408</v>
+        <v>5.073633008845449</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08035417506042689</v>
+        <v>0.08009895458052979</v>
       </c>
       <c r="C42">
-        <v>28.23057458213952</v>
+        <v>27.89760656587515</v>
       </c>
       <c r="D42">
-        <v>39.52671689639988</v>
+        <v>39.61690243799201</v>
       </c>
       <c r="E42">
-        <v>13.71078652860947</v>
+        <v>14.13394008646598</v>
       </c>
       <c r="F42">
-        <v>16.92614231426035</v>
+        <v>17.34929587211686</v>
       </c>
       <c r="G42">
         <v>5.63</v>
@@ -4731,28 +4731,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M42">
-        <v>0.9360156699785975</v>
+        <v>0.9594160617280625</v>
       </c>
       <c r="N42">
-        <v>3.812984330021403</v>
+        <v>3.789583938271938</v>
       </c>
       <c r="O42">
-        <v>1.334544515507491</v>
+        <v>1.326354378395178</v>
       </c>
       <c r="P42">
-        <v>2.478439814513912</v>
+        <v>2.46322955987676</v>
       </c>
       <c r="Q42">
-        <v>5.258439814513912</v>
+        <v>5.24322955987676</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1099602917673781</v>
+        <v>0.1107822111534403</v>
       </c>
       <c r="T42">
-        <v>1.175118275883307</v>
+        <v>1.190172018085201</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.073633008845449</v>
+        <v>4.949885862288243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08009895458052979</v>
+        <v>0.0798437341006327</v>
       </c>
       <c r="C43">
-        <v>27.89760656587515</v>
+        <v>27.56505103172484</v>
       </c>
       <c r="D43">
-        <v>39.61690243799201</v>
+        <v>39.70750046169821</v>
       </c>
       <c r="E43">
-        <v>14.13394008646598</v>
+        <v>14.55709364432249</v>
       </c>
       <c r="F43">
-        <v>17.34929587211686</v>
+        <v>17.77244942997337</v>
       </c>
       <c r="G43">
         <v>5.63</v>
@@ -4813,28 +4813,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M43">
-        <v>0.9594160617280625</v>
+        <v>0.9828164534775274</v>
       </c>
       <c r="N43">
-        <v>3.789583938271938</v>
+        <v>3.766183546522473</v>
       </c>
       <c r="O43">
-        <v>1.326354378395178</v>
+        <v>1.318164241282866</v>
       </c>
       <c r="P43">
-        <v>2.46322955987676</v>
+        <v>2.448019305239608</v>
       </c>
       <c r="Q43">
-        <v>5.24322955987676</v>
+        <v>5.228019305239608</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1107822111534403</v>
+        <v>0.1116324725872978</v>
       </c>
       <c r="T43">
-        <v>1.190172018085201</v>
+        <v>1.205744854845782</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.949885862288243</v>
+        <v>4.832031436995665</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07984373410063271</v>
+        <v>0.07958851362073564</v>
       </c>
       <c r="C44">
-        <v>27.56505103172484</v>
+        <v>27.2329108160325</v>
       </c>
       <c r="D44">
-        <v>39.7075004616982</v>
+        <v>39.79851380386238</v>
       </c>
       <c r="E44">
-        <v>14.55709364432249</v>
+        <v>14.980247202179</v>
       </c>
       <c r="F44">
-        <v>17.77244942997337</v>
+        <v>18.19560298782988</v>
       </c>
       <c r="G44">
         <v>5.63</v>
@@ -4895,28 +4895,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M44">
-        <v>0.9828164534775272</v>
+        <v>1.006216845226992</v>
       </c>
       <c r="N44">
-        <v>3.766183546522473</v>
+        <v>3.742783154773008</v>
       </c>
       <c r="O44">
-        <v>1.318164241282866</v>
+        <v>1.309974104170553</v>
       </c>
       <c r="P44">
-        <v>2.448019305239608</v>
+        <v>2.432809050602455</v>
       </c>
       <c r="Q44">
-        <v>5.228019305239608</v>
+        <v>5.212809050602456</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1116324725872978</v>
+        <v>0.1125125677556765</v>
       </c>
       <c r="T44">
-        <v>1.205744854845782</v>
+        <v>1.221864106931296</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.832031436995667</v>
+        <v>4.719658612879487</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07958851362073564</v>
+        <v>0.07933329314083853</v>
       </c>
       <c r="C45">
-        <v>27.2329108160325</v>
+        <v>26.90118878120648</v>
       </c>
       <c r="D45">
-        <v>39.79851380386238</v>
+        <v>39.88994532689286</v>
       </c>
       <c r="E45">
-        <v>14.980247202179</v>
+        <v>15.40340076003551</v>
       </c>
       <c r="F45">
-        <v>18.19560298782988</v>
+        <v>18.61875654568639</v>
       </c>
       <c r="G45">
         <v>5.63</v>
@@ -4977,28 +4977,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M45">
-        <v>1.006216845226992</v>
+        <v>1.029617236976457</v>
       </c>
       <c r="N45">
-        <v>3.742783154773008</v>
+        <v>3.719382763023543</v>
       </c>
       <c r="O45">
-        <v>1.309974104170553</v>
+        <v>1.30178396705824</v>
       </c>
       <c r="P45">
-        <v>2.432809050602455</v>
+        <v>2.417598795965303</v>
       </c>
       <c r="Q45">
-        <v>5.212809050602456</v>
+        <v>5.197598795965304</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1125125677556765</v>
+        <v>0.1134240948943545</v>
       </c>
       <c r="T45">
-        <v>1.221864106931296</v>
+        <v>1.238559046591292</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.719658612879487</v>
+        <v>4.612393644404953</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07933329314083853</v>
+        <v>0.07907807266094145</v>
       </c>
       <c r="C46">
-        <v>26.90118878120648</v>
+        <v>26.56988781601959</v>
       </c>
       <c r="D46">
-        <v>39.88994532689286</v>
+        <v>39.98179791956249</v>
       </c>
       <c r="E46">
-        <v>15.40340076003551</v>
+        <v>15.82655431789201</v>
       </c>
       <c r="F46">
-        <v>18.61875654568639</v>
+        <v>19.0419101035429</v>
       </c>
       <c r="G46">
         <v>5.63</v>
@@ -5059,28 +5059,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M46">
-        <v>1.029617236976457</v>
+        <v>1.053017628725922</v>
       </c>
       <c r="N46">
-        <v>3.719382763023543</v>
+        <v>3.695982371274078</v>
       </c>
       <c r="O46">
-        <v>1.30178396705824</v>
+        <v>1.293593829945927</v>
       </c>
       <c r="P46">
-        <v>2.417598795965303</v>
+        <v>2.40238854132815</v>
       </c>
       <c r="Q46">
-        <v>5.197598795965304</v>
+        <v>5.18238854132815</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1134240948943545</v>
+        <v>0.114368768474439</v>
       </c>
       <c r="T46">
-        <v>1.238559046591292</v>
+        <v>1.255861074966197</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.612393644404953</v>
+        <v>4.50989600786262</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07907807266094145</v>
+        <v>0.07957035218104437</v>
       </c>
       <c r="C47">
-        <v>26.56988781601959</v>
+        <v>25.9699425378559</v>
       </c>
       <c r="D47">
-        <v>39.98179791956249</v>
+        <v>39.8050061992553</v>
       </c>
       <c r="E47">
-        <v>15.82655431789201</v>
+        <v>16.24970787574852</v>
       </c>
       <c r="F47">
-        <v>19.0419101035429</v>
+        <v>19.46506366139941</v>
       </c>
       <c r="G47">
         <v>5.63</v>
@@ -5141,45 +5141,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M47">
-        <v>1.053017628725922</v>
+        <v>1.125080679628886</v>
       </c>
       <c r="N47">
-        <v>3.695982371274078</v>
+        <v>3.623919320371115</v>
       </c>
       <c r="O47">
-        <v>1.293593829945927</v>
+        <v>1.26837176212989</v>
       </c>
       <c r="P47">
-        <v>2.40238854132815</v>
+        <v>2.355547558241224</v>
       </c>
       <c r="Q47">
-        <v>5.18238854132815</v>
+        <v>5.135547558241225</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.114368768474439</v>
+        <v>0.115348429964897</v>
       </c>
       <c r="T47">
-        <v>1.255861074966197</v>
+        <v>1.27380391920684</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.50989600786262</v>
+        <v>4.221030621169751</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07957035218104437</v>
+        <v>0.07933138170114727</v>
       </c>
       <c r="C48">
-        <v>25.9699425378559</v>
+        <v>25.63241445677423</v>
       </c>
       <c r="D48">
-        <v>39.8050061992553</v>
+        <v>39.89063167603014</v>
       </c>
       <c r="E48">
-        <v>16.24970787574852</v>
+        <v>16.67286143360503</v>
       </c>
       <c r="F48">
-        <v>19.46506366139941</v>
+        <v>19.88821721925591</v>
       </c>
       <c r="G48">
         <v>5.63</v>
@@ -5223,28 +5223,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M48">
-        <v>1.125080679628886</v>
+        <v>1.149538955272992</v>
       </c>
       <c r="N48">
-        <v>3.623919320371115</v>
+        <v>3.599461044727009</v>
       </c>
       <c r="O48">
-        <v>1.26837176212989</v>
+        <v>1.259811365654453</v>
       </c>
       <c r="P48">
-        <v>2.355547558241224</v>
+        <v>2.339649679072556</v>
       </c>
       <c r="Q48">
-        <v>5.135547558241225</v>
+        <v>5.119649679072555</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.115348429964897</v>
+        <v>0.1163650598134854</v>
       </c>
       <c r="T48">
-        <v>1.27380391920684</v>
+        <v>1.292423851909393</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.221030621169751</v>
+        <v>4.131221459017203</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07933138170114727</v>
+        <v>0.07909241122125019</v>
       </c>
       <c r="C49">
-        <v>25.63241445677423</v>
+        <v>25.29525555175419</v>
       </c>
       <c r="D49">
-        <v>39.89063167603014</v>
+        <v>39.97662632886661</v>
       </c>
       <c r="E49">
-        <v>16.67286143360503</v>
+        <v>17.09601499146154</v>
       </c>
       <c r="F49">
-        <v>19.88821721925591</v>
+        <v>20.31137077711242</v>
       </c>
       <c r="G49">
         <v>5.63</v>
@@ -5305,28 +5305,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M49">
-        <v>1.149538955272992</v>
+        <v>1.173997230917098</v>
       </c>
       <c r="N49">
-        <v>3.599461044727009</v>
+        <v>3.575002769082903</v>
       </c>
       <c r="O49">
-        <v>1.259811365654453</v>
+        <v>1.251250969179016</v>
       </c>
       <c r="P49">
-        <v>2.339649679072556</v>
+        <v>2.323751799903887</v>
       </c>
       <c r="Q49">
-        <v>5.119649679072555</v>
+        <v>5.103751799903886</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1163650598134854</v>
+        <v>0.1174207908100965</v>
       </c>
       <c r="T49">
-        <v>1.292423851909393</v>
+        <v>1.311759935869738</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.131221459017203</v>
+        <v>4.045154345287678</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07909241122125019</v>
+        <v>0.07996819074135311</v>
       </c>
       <c r="C50">
-        <v>25.29525555175419</v>
+        <v>24.55874487098151</v>
       </c>
       <c r="D50">
-        <v>39.97662632886661</v>
+        <v>39.66326920595044</v>
       </c>
       <c r="E50">
-        <v>17.09601499146154</v>
+        <v>17.51916854931805</v>
       </c>
       <c r="F50">
-        <v>20.31137077711242</v>
+        <v>20.73452433496893</v>
       </c>
       <c r="G50">
         <v>5.63</v>
@@ -5387,45 +5387,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M50">
-        <v>1.173997230917098</v>
+        <v>1.271026341733595</v>
       </c>
       <c r="N50">
-        <v>3.575002769082903</v>
+        <v>3.477973658266405</v>
       </c>
       <c r="O50">
-        <v>1.251250969179016</v>
+        <v>1.217290780393242</v>
       </c>
       <c r="P50">
-        <v>2.323751799903887</v>
+        <v>2.260682877873164</v>
       </c>
       <c r="Q50">
-        <v>5.103751799903886</v>
+        <v>5.040682877873163</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1174207908100965</v>
+        <v>0.118517923022261</v>
       </c>
       <c r="T50">
-        <v>1.311759935869738</v>
+        <v>1.331854297632448</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.045154345287678</v>
+        <v>3.736350572815573</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07996819074135311</v>
+        <v>0.07975197026145601</v>
       </c>
       <c r="C51">
-        <v>24.55874487098151</v>
+        <v>24.21249820488046</v>
       </c>
       <c r="D51">
-        <v>39.66326920595044</v>
+        <v>39.7401760977059</v>
       </c>
       <c r="E51">
-        <v>17.51916854931805</v>
+        <v>17.94232210717456</v>
       </c>
       <c r="F51">
-        <v>20.73452433496893</v>
+        <v>21.15767789282544</v>
       </c>
       <c r="G51">
         <v>5.63</v>
@@ -5469,28 +5469,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M51">
-        <v>1.271026341733595</v>
+        <v>1.2969656548302</v>
       </c>
       <c r="N51">
-        <v>3.477973658266405</v>
+        <v>3.452034345169801</v>
       </c>
       <c r="O51">
-        <v>1.217290780393242</v>
+        <v>1.20821202080943</v>
       </c>
       <c r="P51">
-        <v>2.260682877873164</v>
+        <v>2.243822324360371</v>
       </c>
       <c r="Q51">
-        <v>5.040682877873163</v>
+        <v>5.023822324360371</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.118517923022261</v>
+        <v>0.119658940522912</v>
       </c>
       <c r="T51">
-        <v>1.331854297632448</v>
+        <v>1.352752433865667</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.736350572815573</v>
+        <v>3.66162356135926</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07975197026145601</v>
+        <v>0.07953574978155893</v>
       </c>
       <c r="C52">
-        <v>24.21249820488046</v>
+        <v>23.86655036239712</v>
       </c>
       <c r="D52">
-        <v>39.7401760977059</v>
+        <v>39.81738181307907</v>
       </c>
       <c r="E52">
-        <v>17.94232210717456</v>
+        <v>18.36547566503107</v>
       </c>
       <c r="F52">
-        <v>21.15767789282544</v>
+        <v>21.58083145068195</v>
       </c>
       <c r="G52">
         <v>5.63</v>
@@ -5551,28 +5551,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M52">
-        <v>1.2969656548302</v>
+        <v>1.322904967926803</v>
       </c>
       <c r="N52">
-        <v>3.452034345169801</v>
+        <v>3.426095032073197</v>
       </c>
       <c r="O52">
-        <v>1.20821202080943</v>
+        <v>1.199133261225619</v>
       </c>
       <c r="P52">
-        <v>2.243822324360371</v>
+        <v>2.226961770847578</v>
       </c>
       <c r="Q52">
-        <v>5.023822324360371</v>
+        <v>5.006961770847578</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.119658940522912</v>
+        <v>0.1208465301664468</v>
       </c>
       <c r="T52">
-        <v>1.352752433865667</v>
+        <v>1.374503555251262</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.66162356135926</v>
+        <v>3.589827020940452</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07953574978155893</v>
+        <v>0.07931952930166185</v>
       </c>
       <c r="C53">
-        <v>23.86655036239712</v>
+        <v>23.52090308855142</v>
       </c>
       <c r="D53">
-        <v>39.81738181307907</v>
+        <v>39.89488809708988</v>
       </c>
       <c r="E53">
-        <v>18.36547566503107</v>
+        <v>18.78862922288758</v>
       </c>
       <c r="F53">
-        <v>21.58083145068195</v>
+        <v>22.00398500853846</v>
       </c>
       <c r="G53">
         <v>5.63</v>
@@ -5633,28 +5633,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M53">
-        <v>1.322904967926803</v>
+        <v>1.348844281023407</v>
       </c>
       <c r="N53">
-        <v>3.426095032073197</v>
+        <v>3.400155718976593</v>
       </c>
       <c r="O53">
-        <v>1.199133261225619</v>
+        <v>1.190054501641808</v>
       </c>
       <c r="P53">
-        <v>2.226961770847578</v>
+        <v>2.210101217334786</v>
       </c>
       <c r="Q53">
-        <v>5.006961770847578</v>
+        <v>4.990101217334786</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1208465301664468</v>
+        <v>0.1220836027117955</v>
       </c>
       <c r="T53">
-        <v>1.374503555251262</v>
+        <v>1.397160973361257</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.589827020940452</v>
+        <v>3.520791885922366</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07931952930166185</v>
+        <v>0.08006790882176476</v>
       </c>
       <c r="C54">
-        <v>23.52090308855142</v>
+        <v>22.83076238531824</v>
       </c>
       <c r="D54">
-        <v>39.89488809708988</v>
+        <v>39.62790095171321</v>
       </c>
       <c r="E54">
-        <v>18.78862922288758</v>
+        <v>19.21178278074408</v>
       </c>
       <c r="F54">
-        <v>22.00398500853846</v>
+        <v>22.42713856639497</v>
       </c>
       <c r="G54">
         <v>5.63</v>
@@ -5715,45 +5715,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M54">
-        <v>1.348844281023407</v>
+        <v>1.437579582105917</v>
       </c>
       <c r="N54">
-        <v>3.400155718976593</v>
+        <v>3.311420417894083</v>
       </c>
       <c r="O54">
-        <v>1.190054501641808</v>
+        <v>1.158997146262929</v>
       </c>
       <c r="P54">
-        <v>2.210101217334786</v>
+        <v>2.152423271631154</v>
       </c>
       <c r="Q54">
-        <v>4.990101217334786</v>
+        <v>4.932423271631153</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1220836027117955</v>
+        <v>0.1233733166420527</v>
       </c>
       <c r="T54">
-        <v>1.397160973361257</v>
+        <v>1.420782536922741</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.35</v>
       </c>
       <c r="W54">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.520791885922366</v>
+        <v>3.303469289013667</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08006790882176476</v>
+        <v>0.07986988834186767</v>
       </c>
       <c r="C55">
-        <v>22.83076238531824</v>
+        <v>22.47790506805098</v>
       </c>
       <c r="D55">
-        <v>39.62790095171321</v>
+        <v>39.69819719230245</v>
       </c>
       <c r="E55">
-        <v>19.21178278074408</v>
+        <v>19.6349363386006</v>
       </c>
       <c r="F55">
-        <v>22.42713856639497</v>
+        <v>22.85029212425148</v>
       </c>
       <c r="G55">
         <v>5.63</v>
@@ -5797,28 +5797,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M55">
-        <v>1.437579582105917</v>
+        <v>1.46470372516452</v>
       </c>
       <c r="N55">
-        <v>3.311420417894083</v>
+        <v>3.284296274835481</v>
       </c>
       <c r="O55">
-        <v>1.158997146262929</v>
+        <v>1.149503696192418</v>
       </c>
       <c r="P55">
-        <v>2.152423271631154</v>
+        <v>2.134792578643062</v>
       </c>
       <c r="Q55">
-        <v>4.932423271631153</v>
+        <v>4.914792578643063</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1233733166420527</v>
+        <v>0.1247191050910167</v>
       </c>
       <c r="T55">
-        <v>1.420782536922741</v>
+        <v>1.445431124986898</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.303469289013667</v>
+        <v>3.24229393180971</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07986988834186767</v>
+        <v>0.07967186786197059</v>
       </c>
       <c r="C56">
-        <v>22.47790506805098</v>
+        <v>22.12529759207097</v>
       </c>
       <c r="D56">
-        <v>39.69819719230245</v>
+        <v>39.76874327417895</v>
       </c>
       <c r="E56">
-        <v>19.6349363386006</v>
+        <v>20.0580898964571</v>
       </c>
       <c r="F56">
-        <v>22.85029212425148</v>
+        <v>23.27344568210799</v>
       </c>
       <c r="G56">
         <v>5.63</v>
@@ -5879,28 +5879,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M56">
-        <v>1.46470372516452</v>
+        <v>1.491827868223122</v>
       </c>
       <c r="N56">
-        <v>3.284296274835481</v>
+        <v>3.257172131776878</v>
       </c>
       <c r="O56">
-        <v>1.149503696192418</v>
+        <v>1.140010246121907</v>
       </c>
       <c r="P56">
-        <v>2.134792578643062</v>
+        <v>2.117161885654971</v>
       </c>
       <c r="Q56">
-        <v>4.914792578643063</v>
+        <v>4.89716188565497</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1247191050910167</v>
+        <v>0.1261247063599346</v>
       </c>
       <c r="T56">
-        <v>1.445431124986898</v>
+        <v>1.471175205853907</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.24229393180971</v>
+        <v>3.183343133049534</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07967186786197059</v>
+        <v>0.0794738473820735</v>
       </c>
       <c r="C57">
-        <v>22.12529759207097</v>
+        <v>21.77294129169833</v>
       </c>
       <c r="D57">
-        <v>39.76874327417895</v>
+        <v>39.83954053166283</v>
       </c>
       <c r="E57">
-        <v>20.0580898964571</v>
+        <v>20.48124345431361</v>
       </c>
       <c r="F57">
-        <v>23.27344568210799</v>
+        <v>23.6965992399645</v>
       </c>
       <c r="G57">
         <v>5.63</v>
@@ -5961,28 +5961,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M57">
-        <v>1.491827868223122</v>
+        <v>1.518952011281724</v>
       </c>
       <c r="N57">
-        <v>3.257172131776878</v>
+        <v>3.230047988718276</v>
       </c>
       <c r="O57">
-        <v>1.140010246121907</v>
+        <v>1.130516796051396</v>
       </c>
       <c r="P57">
-        <v>2.117161885654971</v>
+        <v>2.09953119266688</v>
       </c>
       <c r="Q57">
-        <v>4.89716188565497</v>
+        <v>4.87953119266688</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1261247063599346</v>
+        <v>0.1275941985956216</v>
       </c>
       <c r="T57">
-        <v>1.471175205853907</v>
+        <v>1.498089472214871</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.183343133049534</v>
+        <v>3.126497719959363</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0794738473820735</v>
+        <v>0.07927582690217641</v>
       </c>
       <c r="C58">
-        <v>21.77294129169833</v>
+        <v>21.42083751077167</v>
       </c>
       <c r="D58">
-        <v>39.83954053166283</v>
+        <v>39.91059030859267</v>
       </c>
       <c r="E58">
-        <v>20.48124345431361</v>
+        <v>20.90439701217012</v>
       </c>
       <c r="F58">
-        <v>23.6965992399645</v>
+        <v>24.119752797821</v>
       </c>
       <c r="G58">
         <v>5.63</v>
@@ -6043,28 +6043,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M58">
-        <v>1.518952011281724</v>
+        <v>1.546076154340327</v>
       </c>
       <c r="N58">
-        <v>3.230047988718276</v>
+        <v>3.202923845659674</v>
       </c>
       <c r="O58">
-        <v>1.130516796051396</v>
+        <v>1.121023345980886</v>
       </c>
       <c r="P58">
-        <v>2.09953119266688</v>
+        <v>2.081900499678788</v>
       </c>
       <c r="Q58">
-        <v>4.87953119266688</v>
+        <v>4.861900499678788</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1275941985956216</v>
+        <v>0.129132039307387</v>
       </c>
       <c r="T58">
-        <v>1.498089472214871</v>
+        <v>1.526255564918205</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.126497719959363</v>
+        <v>3.071646882767094</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07927582690217641</v>
+        <v>0.07907780642227934</v>
       </c>
       <c r="C59">
-        <v>21.42083751077167</v>
+        <v>21.06898760273311</v>
       </c>
       <c r="D59">
-        <v>39.91059030859267</v>
+        <v>39.98189395841062</v>
       </c>
       <c r="E59">
-        <v>20.90439701217012</v>
+        <v>21.32755057002663</v>
       </c>
       <c r="F59">
-        <v>24.119752797821</v>
+        <v>24.54290635567751</v>
       </c>
       <c r="G59">
         <v>5.63</v>
@@ -6125,28 +6125,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M59">
-        <v>1.546076154340327</v>
+        <v>1.573200297398929</v>
       </c>
       <c r="N59">
-        <v>3.202923845659674</v>
+        <v>3.175799702601072</v>
       </c>
       <c r="O59">
-        <v>1.121023345980886</v>
+        <v>1.111529895910375</v>
       </c>
       <c r="P59">
-        <v>2.081900499678788</v>
+        <v>2.064269806690697</v>
       </c>
       <c r="Q59">
-        <v>4.861900499678788</v>
+        <v>4.844269806690697</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.129132039307387</v>
+        <v>0.1307431105292365</v>
       </c>
       <c r="T59">
-        <v>1.526255564918205</v>
+        <v>1.555762900131222</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.071646882767094</v>
+        <v>3.018687453753869</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07907780642227934</v>
+        <v>0.08187108594238225</v>
       </c>
       <c r="C60">
-        <v>21.06898760273312</v>
+        <v>19.66299592884371</v>
       </c>
       <c r="D60">
-        <v>39.98189395841062</v>
+        <v>38.99905584237772</v>
       </c>
       <c r="E60">
-        <v>21.32755057002663</v>
+        <v>21.75070412788314</v>
       </c>
       <c r="F60">
-        <v>24.54290635567751</v>
+        <v>24.96605991353402</v>
       </c>
       <c r="G60">
         <v>5.63</v>
@@ -6207,45 +6207,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M60">
-        <v>1.573200297398929</v>
+        <v>1.795059707783096</v>
       </c>
       <c r="N60">
-        <v>3.175799702601072</v>
+        <v>2.953940292216904</v>
       </c>
       <c r="O60">
-        <v>1.111529895910375</v>
+        <v>1.033879102275916</v>
       </c>
       <c r="P60">
-        <v>2.064269806690697</v>
+        <v>1.920061189940988</v>
       </c>
       <c r="Q60">
-        <v>4.844269806690697</v>
+        <v>4.700061189940987</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1307431105292365</v>
+        <v>0.1324327705911762</v>
       </c>
       <c r="T60">
-        <v>1.555762900131221</v>
+        <v>1.586709617549751</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.018687453753869</v>
+        <v>2.645594449816396</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08187108594238225</v>
+        <v>0.08172376546248517</v>
       </c>
       <c r="C61">
-        <v>19.66299592884371</v>
+        <v>19.29046968301927</v>
       </c>
       <c r="D61">
-        <v>38.99905584237772</v>
+        <v>39.0496831544098</v>
       </c>
       <c r="E61">
-        <v>21.75070412788314</v>
+        <v>22.17385768573964</v>
       </c>
       <c r="F61">
-        <v>24.96605991353402</v>
+        <v>25.38921347139053</v>
       </c>
       <c r="G61">
         <v>5.63</v>
@@ -6289,28 +6289,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M61">
-        <v>1.795059707783096</v>
+        <v>1.825484448592979</v>
       </c>
       <c r="N61">
-        <v>2.953940292216904</v>
+        <v>2.923515551407021</v>
       </c>
       <c r="O61">
-        <v>1.033879102275916</v>
+        <v>1.023230442992457</v>
       </c>
       <c r="P61">
-        <v>1.920061189940988</v>
+        <v>1.900285108414564</v>
       </c>
       <c r="Q61">
-        <v>4.700061189940987</v>
+        <v>4.680285108414564</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1324327705911762</v>
+        <v>0.1342069136562129</v>
       </c>
       <c r="T61">
-        <v>1.586709617549751</v>
+        <v>1.619203670839207</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.645594449816396</v>
+        <v>2.601501208986122</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08172376546248517</v>
+        <v>0.08157644498258806</v>
       </c>
       <c r="C62">
-        <v>19.29046968301927</v>
+        <v>18.91807505353061</v>
       </c>
       <c r="D62">
-        <v>39.0496831544098</v>
+        <v>39.10044208277765</v>
       </c>
       <c r="E62">
-        <v>22.17385768573964</v>
+        <v>22.59701124359615</v>
       </c>
       <c r="F62">
-        <v>25.38921347139053</v>
+        <v>25.81236702924704</v>
       </c>
       <c r="G62">
         <v>5.63</v>
@@ -6371,28 +6371,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M62">
-        <v>1.825484448592979</v>
+        <v>1.855909189402862</v>
       </c>
       <c r="N62">
-        <v>2.923515551407021</v>
+        <v>2.893090810597139</v>
       </c>
       <c r="O62">
-        <v>1.023230442992457</v>
+        <v>1.012581783708999</v>
       </c>
       <c r="P62">
-        <v>1.900285108414564</v>
+        <v>1.88050902688814</v>
       </c>
       <c r="Q62">
-        <v>4.680285108414564</v>
+        <v>4.66050902688814</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1342069136562129</v>
+        <v>0.1360720384168925</v>
       </c>
       <c r="T62">
-        <v>1.619203670839207</v>
+        <v>1.653364085835815</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.601501208986122</v>
+        <v>2.558853648183072</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08157644498258806</v>
+        <v>0.08142912450269099</v>
       </c>
       <c r="C63">
-        <v>18.91807505353061</v>
+        <v>18.54581255429221</v>
       </c>
       <c r="D63">
-        <v>39.10044208277765</v>
+        <v>39.15133314139575</v>
       </c>
       <c r="E63">
-        <v>22.59701124359615</v>
+        <v>23.02016480145266</v>
       </c>
       <c r="F63">
-        <v>25.81236702924704</v>
+        <v>26.23552058710354</v>
       </c>
       <c r="G63">
         <v>5.63</v>
@@ -6453,28 +6453,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M63">
-        <v>1.855909189402862</v>
+        <v>1.886333930212745</v>
       </c>
       <c r="N63">
-        <v>2.893090810597139</v>
+        <v>2.862666069787256</v>
       </c>
       <c r="O63">
-        <v>1.012581783708999</v>
+        <v>1.00193312442554</v>
       </c>
       <c r="P63">
-        <v>1.88050902688814</v>
+        <v>1.860732945361716</v>
       </c>
       <c r="Q63">
-        <v>4.66050902688814</v>
+        <v>4.640732945361716</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1360720384168925</v>
+        <v>0.1380353276386605</v>
       </c>
       <c r="T63">
-        <v>1.653364085835815</v>
+        <v>1.689322417411192</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.558853648183072</v>
+        <v>2.517581815147861</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08142912450269099</v>
+        <v>0.08287885402279391</v>
       </c>
       <c r="C64">
-        <v>18.54581255429221</v>
+        <v>17.62754742486837</v>
       </c>
       <c r="D64">
-        <v>39.15133314139575</v>
+        <v>38.65622156982842</v>
       </c>
       <c r="E64">
-        <v>23.02016480145266</v>
+        <v>23.44331835930917</v>
       </c>
       <c r="F64">
-        <v>26.23552058710354</v>
+        <v>26.65867414496006</v>
       </c>
       <c r="G64">
         <v>5.63</v>
@@ -6535,45 +6535,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M64">
-        <v>1.886333930212745</v>
+        <v>2.020727500187972</v>
       </c>
       <c r="N64">
-        <v>2.862666069787256</v>
+        <v>2.728272499812028</v>
       </c>
       <c r="O64">
-        <v>1.00193312442554</v>
+        <v>0.9548953749342098</v>
       </c>
       <c r="P64">
-        <v>1.860732945361716</v>
+        <v>1.773377124877818</v>
       </c>
       <c r="Q64">
-        <v>4.640732945361716</v>
+        <v>4.553377124877818</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1380353276386605</v>
+        <v>0.1401047406021457</v>
       </c>
       <c r="T64">
-        <v>1.689322417411192</v>
+        <v>1.727224442585237</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.517581815147861</v>
+        <v>2.350143698028675</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08287885402279391</v>
+        <v>0.08275688354289681</v>
       </c>
       <c r="C65">
-        <v>17.62754742486837</v>
+        <v>17.24556624875511</v>
       </c>
       <c r="D65">
-        <v>38.65622156982842</v>
+        <v>38.69739395157167</v>
       </c>
       <c r="E65">
-        <v>23.44331835930917</v>
+        <v>23.86647191716568</v>
       </c>
       <c r="F65">
-        <v>26.65867414496006</v>
+        <v>27.08182770281656</v>
       </c>
       <c r="G65">
         <v>5.63</v>
@@ -6617,28 +6617,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M65">
-        <v>2.020727500187972</v>
+        <v>2.052802539873496</v>
       </c>
       <c r="N65">
-        <v>2.728272499812028</v>
+        <v>2.696197460126505</v>
       </c>
       <c r="O65">
-        <v>0.9548953749342098</v>
+        <v>0.9436691110442765</v>
       </c>
       <c r="P65">
-        <v>1.773377124877818</v>
+        <v>1.752528349082228</v>
       </c>
       <c r="Q65">
-        <v>4.553377124877818</v>
+        <v>4.532528349082228</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1401047406021457</v>
+        <v>0.1422891209524912</v>
       </c>
       <c r="T65">
-        <v>1.727224442585237</v>
+        <v>1.767232135824508</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.350143698028675</v>
+        <v>2.313422702746976</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08275688354289681</v>
+        <v>0.08263491306299972</v>
       </c>
       <c r="C66">
-        <v>17.24556624875511</v>
+        <v>16.86367287079588</v>
       </c>
       <c r="D66">
-        <v>38.69739395157167</v>
+        <v>38.73865413146896</v>
       </c>
       <c r="E66">
-        <v>23.86647191716568</v>
+        <v>24.28962547502219</v>
       </c>
       <c r="F66">
-        <v>27.08182770281656</v>
+        <v>27.50498126067307</v>
       </c>
       <c r="G66">
         <v>5.63</v>
@@ -6699,28 +6699,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M66">
-        <v>2.052802539873496</v>
+        <v>2.084877579559019</v>
       </c>
       <c r="N66">
-        <v>2.696197460126505</v>
+        <v>2.664122420440981</v>
       </c>
       <c r="O66">
-        <v>0.9436691110442765</v>
+        <v>0.9324428471543434</v>
       </c>
       <c r="P66">
-        <v>1.752528349082228</v>
+        <v>1.731679573286638</v>
       </c>
       <c r="Q66">
-        <v>4.532528349082228</v>
+        <v>4.511679573286638</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1422891209524912</v>
+        <v>0.1445983230371421</v>
       </c>
       <c r="T66">
-        <v>1.767232135824508</v>
+        <v>1.809525982963165</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.313422702746976</v>
+        <v>2.277831584243177</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08263491306299972</v>
+        <v>0.08251294258310263</v>
       </c>
       <c r="C67">
-        <v>16.86367287079588</v>
+        <v>16.48186757212855</v>
       </c>
       <c r="D67">
-        <v>38.73865413146896</v>
+        <v>38.78000239065813</v>
       </c>
       <c r="E67">
-        <v>24.28962547502219</v>
+        <v>24.7127790328787</v>
       </c>
       <c r="F67">
-        <v>27.50498126067307</v>
+        <v>27.92813481852958</v>
       </c>
       <c r="G67">
         <v>5.63</v>
@@ -6781,28 +6781,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M67">
-        <v>2.084877579559019</v>
+        <v>2.116952619244543</v>
       </c>
       <c r="N67">
-        <v>2.664122420440981</v>
+        <v>2.632047380755458</v>
       </c>
       <c r="O67">
-        <v>0.9324428471543434</v>
+        <v>0.9212165832644101</v>
       </c>
       <c r="P67">
-        <v>1.731679573286638</v>
+        <v>1.710830797491048</v>
       </c>
       <c r="Q67">
-        <v>4.511679573286638</v>
+        <v>4.490830797491047</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1445983230371421</v>
+        <v>0.1470433605385372</v>
       </c>
       <c r="T67">
-        <v>1.809525982963165</v>
+        <v>1.854307703462919</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.277831584243177</v>
+        <v>2.243318984481916</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08251294258310263</v>
+        <v>0.08239097210320556</v>
       </c>
       <c r="C68">
-        <v>16.48186757212855</v>
+        <v>16.10015063509259</v>
       </c>
       <c r="D68">
-        <v>38.78000239065813</v>
+        <v>38.82143901147868</v>
       </c>
       <c r="E68">
-        <v>24.7127790328787</v>
+        <v>25.13593259073521</v>
       </c>
       <c r="F68">
-        <v>27.92813481852958</v>
+        <v>28.35128837638609</v>
       </c>
       <c r="G68">
         <v>5.63</v>
@@ -6863,28 +6863,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M68">
-        <v>2.116952619244543</v>
+        <v>2.149027658930066</v>
       </c>
       <c r="N68">
-        <v>2.632047380755458</v>
+        <v>2.599972341069935</v>
       </c>
       <c r="O68">
-        <v>0.9212165832644101</v>
+        <v>0.9099903193744771</v>
       </c>
       <c r="P68">
-        <v>1.710830797491048</v>
+        <v>1.689982021695458</v>
       </c>
       <c r="Q68">
-        <v>4.490830797491047</v>
+        <v>4.469982021695458</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1470433605385372</v>
+        <v>0.149636582130926</v>
       </c>
       <c r="T68">
-        <v>1.854307703462919</v>
+        <v>1.901803467629326</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.243318984481916</v>
+        <v>2.209836611579202</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08239097210320556</v>
+        <v>0.08226900162330847</v>
       </c>
       <c r="C69">
-        <v>16.10015063509259</v>
+        <v>15.71852234323545</v>
       </c>
       <c r="D69">
-        <v>38.82143901147868</v>
+        <v>38.86296427747804</v>
       </c>
       <c r="E69">
-        <v>25.13593259073521</v>
+        <v>25.55908614859172</v>
       </c>
       <c r="F69">
-        <v>28.35128837638609</v>
+        <v>28.7744419342426</v>
       </c>
       <c r="G69">
         <v>5.63</v>
@@ -6945,28 +6945,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M69">
-        <v>2.149027658930066</v>
+        <v>2.181102698615589</v>
       </c>
       <c r="N69">
-        <v>2.599972341069935</v>
+        <v>2.567897301384412</v>
       </c>
       <c r="O69">
-        <v>0.9099903193744771</v>
+        <v>0.898764055484544</v>
       </c>
       <c r="P69">
-        <v>1.689982021695458</v>
+        <v>1.669133245899868</v>
       </c>
       <c r="Q69">
-        <v>4.469982021695458</v>
+        <v>4.449133245899867</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.149636582130926</v>
+        <v>0.152391880072839</v>
       </c>
       <c r="T69">
-        <v>1.901803467629326</v>
+        <v>1.952267717056133</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.209836611579202</v>
+        <v>2.177339014350096</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08226900162330847</v>
+        <v>0.08214703114341138</v>
       </c>
       <c r="C70">
-        <v>15.71852234323545</v>
+        <v>15.33698298131908</v>
       </c>
       <c r="D70">
-        <v>38.86296427747804</v>
+        <v>38.90457847341818</v>
       </c>
       <c r="E70">
-        <v>25.55908614859172</v>
+        <v>25.98223970644823</v>
       </c>
       <c r="F70">
-        <v>28.7744419342426</v>
+        <v>29.19759549209911</v>
       </c>
       <c r="G70">
         <v>5.63</v>
@@ -7027,28 +7027,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M70">
-        <v>2.181102698615589</v>
+        <v>2.213177738301113</v>
       </c>
       <c r="N70">
-        <v>2.567897301384412</v>
+        <v>2.535822261698888</v>
       </c>
       <c r="O70">
-        <v>0.898764055484544</v>
+        <v>0.8875377915946107</v>
       </c>
       <c r="P70">
-        <v>1.669133245899868</v>
+        <v>1.648284470104277</v>
       </c>
       <c r="Q70">
-        <v>4.449133245899867</v>
+        <v>4.428284470104277</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.152391880072839</v>
+        <v>0.1553249391722948</v>
       </c>
       <c r="T70">
-        <v>1.952267717056133</v>
+        <v>2.005987724510476</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.177339014350096</v>
+        <v>2.145783376460964</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08214703114341138</v>
+        <v>0.0820250606635143</v>
       </c>
       <c r="C71">
-        <v>15.33698298131908</v>
+        <v>14.95553283532642</v>
       </c>
       <c r="D71">
-        <v>38.90457847341818</v>
+        <v>38.94628188528203</v>
       </c>
       <c r="E71">
-        <v>25.98223970644823</v>
+        <v>26.40539326430474</v>
       </c>
       <c r="F71">
-        <v>29.19759549209911</v>
+        <v>29.62074904995562</v>
       </c>
       <c r="G71">
         <v>5.63</v>
@@ -7109,28 +7109,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M71">
-        <v>2.213177738301113</v>
+        <v>2.245252777986636</v>
       </c>
       <c r="N71">
-        <v>2.535822261698888</v>
+        <v>2.503747222013364</v>
       </c>
       <c r="O71">
-        <v>0.8875377915946107</v>
+        <v>0.8763115277046775</v>
       </c>
       <c r="P71">
-        <v>1.648284470104277</v>
+        <v>1.627435694308687</v>
       </c>
       <c r="Q71">
-        <v>4.428284470104277</v>
+        <v>4.407435694308687</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1553249391722948</v>
+        <v>0.1584535355450477</v>
       </c>
       <c r="T71">
-        <v>2.005987724510476</v>
+        <v>2.063289065795108</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.145783376460964</v>
+        <v>2.115129328225807</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0820250606635143</v>
+        <v>0.08190309018361722</v>
       </c>
       <c r="C72">
-        <v>14.95553283532642</v>
+        <v>14.57417219246798</v>
       </c>
       <c r="D72">
-        <v>38.94628188528203</v>
+        <v>38.9880748002801</v>
       </c>
       <c r="E72">
-        <v>26.40539326430474</v>
+        <v>26.82854682216125</v>
       </c>
       <c r="F72">
-        <v>29.62074904995562</v>
+        <v>30.04390260781213</v>
       </c>
       <c r="G72">
         <v>5.63</v>
@@ -7191,28 +7191,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M72">
-        <v>2.245252777986636</v>
+        <v>2.277327817672159</v>
       </c>
       <c r="N72">
-        <v>2.503747222013364</v>
+        <v>2.471672182327841</v>
       </c>
       <c r="O72">
-        <v>0.8763115277046775</v>
+        <v>0.8650852638147444</v>
       </c>
       <c r="P72">
-        <v>1.627435694308687</v>
+        <v>1.606586918513097</v>
       </c>
       <c r="Q72">
-        <v>4.407435694308687</v>
+        <v>4.386586918513096</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1584535355450477</v>
+        <v>0.161797897184887</v>
       </c>
       <c r="T72">
-        <v>2.063289065795108</v>
+        <v>2.12454222372006</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.115129328225807</v>
+        <v>2.085338774307134</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08190309018361722</v>
+        <v>0.08178111970372012</v>
       </c>
       <c r="C73">
-        <v>14.57417219246798</v>
+        <v>14.19290134118836</v>
       </c>
       <c r="D73">
-        <v>38.9880748002801</v>
+        <v>39.02995750685699</v>
       </c>
       <c r="E73">
-        <v>26.82854682216124</v>
+        <v>27.25170038001775</v>
       </c>
       <c r="F73">
-        <v>30.04390260781212</v>
+        <v>30.46705616566863</v>
       </c>
       <c r="G73">
         <v>5.63</v>
@@ -7273,28 +7273,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M73">
-        <v>2.277327817672159</v>
+        <v>2.309402857357683</v>
       </c>
       <c r="N73">
-        <v>2.471672182327842</v>
+        <v>2.439597142642318</v>
       </c>
       <c r="O73">
-        <v>0.8650852638147445</v>
+        <v>0.8538589999248113</v>
       </c>
       <c r="P73">
-        <v>1.606586918513097</v>
+        <v>1.585738142717507</v>
       </c>
       <c r="Q73">
-        <v>4.386586918513097</v>
+        <v>4.365738142717507</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1617978971848869</v>
+        <v>0.1653811417990004</v>
       </c>
       <c r="T73">
-        <v>2.12454222372006</v>
+        <v>2.190170607211079</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.085338774307134</v>
+        <v>2.05637573577509</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08178111970372012</v>
+        <v>0.08165914922382304</v>
       </c>
       <c r="C74">
-        <v>14.19290134118836</v>
+        <v>13.81172057117296</v>
       </c>
       <c r="D74">
-        <v>39.02995750685699</v>
+        <v>39.0719302946981</v>
       </c>
       <c r="E74">
-        <v>27.25170038001775</v>
+        <v>27.67485393787426</v>
       </c>
       <c r="F74">
-        <v>30.46705616566863</v>
+        <v>30.89020972352514</v>
       </c>
       <c r="G74">
         <v>5.63</v>
@@ -7355,28 +7355,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M74">
-        <v>2.309402857357683</v>
+        <v>2.341477897043206</v>
       </c>
       <c r="N74">
-        <v>2.439597142642318</v>
+        <v>2.407522102956794</v>
       </c>
       <c r="O74">
-        <v>0.8538589999248113</v>
+        <v>0.842632736034878</v>
       </c>
       <c r="P74">
-        <v>1.585738142717507</v>
+        <v>1.564889366921916</v>
       </c>
       <c r="Q74">
-        <v>4.365738142717507</v>
+        <v>4.344889366921916</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1653811417990004</v>
+        <v>0.1692298119400853</v>
       </c>
       <c r="T74">
-        <v>2.190170607211079</v>
+        <v>2.260660352442175</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.05637573577509</v>
+        <v>2.028206205148034</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08165914922382304</v>
+        <v>0.08153717874392596</v>
       </c>
       <c r="C75">
-        <v>13.81172057117296</v>
+        <v>13.43063017335463</v>
       </c>
       <c r="D75">
-        <v>39.0719302946981</v>
+        <v>39.11399345473627</v>
       </c>
       <c r="E75">
-        <v>27.67485393787426</v>
+        <v>28.09800749573077</v>
       </c>
       <c r="F75">
-        <v>30.89020972352514</v>
+        <v>31.31336328138165</v>
       </c>
       <c r="G75">
         <v>5.63</v>
@@ -7437,28 +7437,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M75">
-        <v>2.341477897043206</v>
+        <v>2.373552936728729</v>
       </c>
       <c r="N75">
-        <v>2.407522102956794</v>
+        <v>2.375447063271271</v>
       </c>
       <c r="O75">
-        <v>0.842632736034878</v>
+        <v>0.8314064721449449</v>
       </c>
       <c r="P75">
-        <v>1.564889366921916</v>
+        <v>1.544040591126326</v>
       </c>
       <c r="Q75">
-        <v>4.344889366921916</v>
+        <v>4.324040591126327</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1692298119400853</v>
+        <v>0.1733745336304844</v>
       </c>
       <c r="T75">
-        <v>2.260660352442175</v>
+        <v>2.336572385767969</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.028206205148034</v>
+        <v>2.000798013186574</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08153717874392596</v>
+        <v>0.08833770826402887</v>
       </c>
       <c r="C76">
-        <v>13.43063017335463</v>
+        <v>10.79264108554724</v>
       </c>
       <c r="D76">
-        <v>39.11399345473627</v>
+        <v>36.8991579247854</v>
       </c>
       <c r="E76">
-        <v>28.09800749573077</v>
+        <v>28.52116105358728</v>
       </c>
       <c r="F76">
-        <v>31.31336328138165</v>
+        <v>31.73651683923816</v>
       </c>
       <c r="G76">
         <v>5.63</v>
@@ -7519,45 +7519,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M76">
-        <v>2.373552936728729</v>
+        <v>2.856286515531434</v>
       </c>
       <c r="N76">
-        <v>2.375447063271271</v>
+        <v>1.892713484468566</v>
       </c>
       <c r="O76">
-        <v>0.8314064721449449</v>
+        <v>0.6624497195639981</v>
       </c>
       <c r="P76">
-        <v>1.544040591126326</v>
+        <v>1.230263764904568</v>
       </c>
       <c r="Q76">
-        <v>4.324040591126327</v>
+        <v>4.010263764904568</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1733745336304844</v>
+        <v>0.1778508330561155</v>
       </c>
       <c r="T76">
-        <v>2.336572385767969</v>
+        <v>2.418557381759828</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.35</v>
       </c>
       <c r="W76">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.000798013186574</v>
+        <v>1.66264832823202</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08833770826402887</v>
+        <v>0.08830803778413178</v>
       </c>
       <c r="C77">
-        <v>10.79264108554724</v>
+        <v>10.37860584972238</v>
       </c>
       <c r="D77">
-        <v>36.8991579247854</v>
+        <v>36.90827624681705</v>
       </c>
       <c r="E77">
-        <v>28.52116105358728</v>
+        <v>28.94431461144379</v>
       </c>
       <c r="F77">
-        <v>31.73651683923816</v>
+        <v>32.15967039709467</v>
       </c>
       <c r="G77">
         <v>5.63</v>
@@ -7601,28 +7601,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M77">
-        <v>2.856286515531434</v>
+        <v>2.89437033573852</v>
       </c>
       <c r="N77">
-        <v>1.892713484468566</v>
+        <v>1.85462966426148</v>
       </c>
       <c r="O77">
-        <v>0.6624497195639981</v>
+        <v>0.649120382491518</v>
       </c>
       <c r="P77">
-        <v>1.230263764904568</v>
+        <v>1.205509281769962</v>
       </c>
       <c r="Q77">
-        <v>4.010263764904568</v>
+        <v>3.985509281769962</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1778508330561155</v>
+        <v>0.1827001574338824</v>
       </c>
       <c r="T77">
-        <v>2.418557381759828</v>
+        <v>2.507374460751009</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.66264832823202</v>
+        <v>1.640771376544756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08830803778413178</v>
+        <v>0.08827836730423469</v>
       </c>
       <c r="C78">
-        <v>10.37860584972238</v>
+        <v>9.964575121553111</v>
       </c>
       <c r="D78">
-        <v>36.90827624681705</v>
+        <v>36.91739907650429</v>
       </c>
       <c r="E78">
-        <v>28.94431461144379</v>
+        <v>29.3674681693003</v>
       </c>
       <c r="F78">
-        <v>32.15967039709467</v>
+        <v>32.58282395495118</v>
       </c>
       <c r="G78">
         <v>5.63</v>
@@ -7683,28 +7683,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M78">
-        <v>2.89437033573852</v>
+        <v>2.932454155945606</v>
       </c>
       <c r="N78">
-        <v>1.85462966426148</v>
+        <v>1.816545844054394</v>
       </c>
       <c r="O78">
-        <v>0.649120382491518</v>
+        <v>0.635791045419038</v>
       </c>
       <c r="P78">
-        <v>1.205509281769962</v>
+        <v>1.180754798635356</v>
       </c>
       <c r="Q78">
-        <v>3.985509281769962</v>
+        <v>3.960754798635356</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1827001574338824</v>
+        <v>0.1879711621923248</v>
       </c>
       <c r="T78">
-        <v>2.507374460751009</v>
+        <v>2.603914764002291</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.640771376544756</v>
+        <v>1.61946265736885</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08827836730423469</v>
+        <v>0.0882486968243376</v>
       </c>
       <c r="C79">
-        <v>9.964575121553111</v>
+        <v>9.550548904382815</v>
       </c>
       <c r="D79">
-        <v>36.91739907650429</v>
+        <v>36.9265264171905</v>
       </c>
       <c r="E79">
-        <v>29.3674681693003</v>
+        <v>29.79062172715681</v>
       </c>
       <c r="F79">
-        <v>32.58282395495118</v>
+        <v>33.00597751280769</v>
       </c>
       <c r="G79">
         <v>5.63</v>
@@ -7765,28 +7765,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M79">
-        <v>2.932454155945606</v>
+        <v>2.970537976152692</v>
       </c>
       <c r="N79">
-        <v>1.816545844054394</v>
+        <v>1.778462023847309</v>
       </c>
       <c r="O79">
-        <v>0.635791045419038</v>
+        <v>0.622461708346558</v>
       </c>
       <c r="P79">
-        <v>1.180754798635356</v>
+        <v>1.156000315500751</v>
       </c>
       <c r="Q79">
-        <v>3.960754798635356</v>
+        <v>3.936000315500751</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1879711621923248</v>
+        <v>0.1937213492015346</v>
       </c>
       <c r="T79">
-        <v>2.603914764002291</v>
+        <v>2.709231458458236</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.61946265736885</v>
+        <v>1.598700315607712</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0882486968243376</v>
+        <v>0.08821902634444051</v>
       </c>
       <c r="C80">
-        <v>9.550548904382815</v>
+        <v>9.136527201558167</v>
       </c>
       <c r="D80">
-        <v>36.9265264171905</v>
+        <v>36.93565827222236</v>
       </c>
       <c r="E80">
-        <v>29.79062172715681</v>
+        <v>30.21377528501332</v>
       </c>
       <c r="F80">
-        <v>33.00597751280769</v>
+        <v>33.4291310706642</v>
       </c>
       <c r="G80">
         <v>5.63</v>
@@ -7847,28 +7847,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M80">
-        <v>2.970537976152692</v>
+        <v>3.008621796359778</v>
       </c>
       <c r="N80">
-        <v>1.778462023847309</v>
+        <v>1.740378203640223</v>
       </c>
       <c r="O80">
-        <v>0.622461708346558</v>
+        <v>0.6091323712740779</v>
       </c>
       <c r="P80">
-        <v>1.156000315500751</v>
+        <v>1.131245832366145</v>
       </c>
       <c r="Q80">
-        <v>3.936000315500751</v>
+        <v>3.911245832366145</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1937213492015346</v>
+        <v>0.2000191730687644</v>
       </c>
       <c r="T80">
-        <v>2.709231458458236</v>
+        <v>2.824578314290938</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.598700315607712</v>
+        <v>1.578463602751917</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08821902634444051</v>
+        <v>0.08818935586454343</v>
       </c>
       <c r="C81">
-        <v>9.136527201558167</v>
+        <v>8.722510016429162</v>
       </c>
       <c r="D81">
-        <v>36.93565827222236</v>
+        <v>36.94479464494987</v>
       </c>
       <c r="E81">
-        <v>30.21377528501332</v>
+        <v>30.63692884286982</v>
       </c>
       <c r="F81">
-        <v>33.4291310706642</v>
+        <v>33.85228462852071</v>
       </c>
       <c r="G81">
         <v>5.63</v>
@@ -7929,28 +7929,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M81">
-        <v>3.008621796359778</v>
+        <v>3.046705616566864</v>
       </c>
       <c r="N81">
-        <v>1.740378203640223</v>
+        <v>1.702294383433137</v>
       </c>
       <c r="O81">
-        <v>0.6091323712740779</v>
+        <v>0.5958030342015979</v>
       </c>
       <c r="P81">
-        <v>1.131245832366145</v>
+        <v>1.106491349231539</v>
       </c>
       <c r="Q81">
-        <v>3.911245832366145</v>
+        <v>3.886491349231539</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2000191730687644</v>
+        <v>0.2069467793227172</v>
       </c>
       <c r="T81">
-        <v>2.824578314290938</v>
+        <v>2.95145985570691</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.578463602751917</v>
+        <v>1.558732807717519</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08818935586454343</v>
+        <v>0.08815968538464636</v>
       </c>
       <c r="C82">
-        <v>8.722510016429162</v>
+        <v>8.308497352349107</v>
       </c>
       <c r="D82">
-        <v>36.94479464494987</v>
+        <v>36.95393553872632</v>
       </c>
       <c r="E82">
-        <v>30.63692884286982</v>
+        <v>31.06008240072633</v>
       </c>
       <c r="F82">
-        <v>33.85228462852071</v>
+        <v>34.27543818637722</v>
       </c>
       <c r="G82">
         <v>5.63</v>
@@ -8011,28 +8011,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M82">
-        <v>3.046705616566864</v>
+        <v>3.084789436773949</v>
       </c>
       <c r="N82">
-        <v>1.702294383433137</v>
+        <v>1.664210563226051</v>
       </c>
       <c r="O82">
-        <v>0.5958030342015979</v>
+        <v>0.5824736971291179</v>
       </c>
       <c r="P82">
-        <v>1.106491349231539</v>
+        <v>1.081736866096934</v>
       </c>
       <c r="Q82">
-        <v>3.886491349231539</v>
+        <v>3.861736866096933</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2069467793227172</v>
+        <v>0.2146036072876124</v>
       </c>
       <c r="T82">
-        <v>2.95145985570691</v>
+        <v>3.091697348850879</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.558732807717519</v>
+        <v>1.539489192807426</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08815968538464636</v>
+        <v>0.08813001490474925</v>
       </c>
       <c r="C83">
-        <v>8.308497352349107</v>
+        <v>7.894489212674642</v>
       </c>
       <c r="D83">
-        <v>36.95393553872632</v>
+        <v>36.96308095690836</v>
       </c>
       <c r="E83">
-        <v>31.06008240072633</v>
+        <v>31.48323595858284</v>
       </c>
       <c r="F83">
-        <v>34.27543818637722</v>
+        <v>34.69859174423372</v>
       </c>
       <c r="G83">
         <v>5.63</v>
@@ -8093,28 +8093,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M83">
-        <v>3.084789436773949</v>
+        <v>3.122873256981035</v>
       </c>
       <c r="N83">
-        <v>1.664210563226051</v>
+        <v>1.626126743018966</v>
       </c>
       <c r="O83">
-        <v>0.5824736971291179</v>
+        <v>0.5691443600566379</v>
       </c>
       <c r="P83">
-        <v>1.081736866096934</v>
+        <v>1.056982382962328</v>
       </c>
       <c r="Q83">
-        <v>3.861736866096933</v>
+        <v>3.836982382962328</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2146036072876124</v>
+        <v>0.2231111939152737</v>
       </c>
       <c r="T83">
-        <v>3.091697348850879</v>
+        <v>3.247516785677511</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.539489192807426</v>
+        <v>1.520714934358555</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08813001490474925</v>
+        <v>0.08810034442485218</v>
       </c>
       <c r="C84">
-        <v>7.894489212674642</v>
+        <v>7.480485600765711</v>
       </c>
       <c r="D84">
-        <v>36.96308095690836</v>
+        <v>36.97223090285594</v>
       </c>
       <c r="E84">
-        <v>31.48323595858284</v>
+        <v>31.90638951643935</v>
       </c>
       <c r="F84">
-        <v>34.69859174423372</v>
+        <v>35.12174530209023</v>
       </c>
       <c r="G84">
         <v>5.63</v>
@@ -8175,28 +8175,28 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M84">
-        <v>3.122873256981035</v>
+        <v>3.160957077188121</v>
       </c>
       <c r="N84">
-        <v>1.626126743018966</v>
+        <v>1.58804292281188</v>
       </c>
       <c r="O84">
-        <v>0.5691443600566379</v>
+        <v>0.5558150229841577</v>
       </c>
       <c r="P84">
-        <v>1.056982382962328</v>
+        <v>1.032227899827722</v>
       </c>
       <c r="Q84">
-        <v>3.836982382962328</v>
+        <v>3.812227899827722</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2231111939152737</v>
+        <v>0.2326196730873658</v>
       </c>
       <c r="T84">
-        <v>3.247516785677511</v>
+        <v>3.421667920954335</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.520714934358555</v>
+        <v>1.502393067679536</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08810034442485218</v>
+        <v>0.1241454520078347</v>
       </c>
       <c r="C85">
-        <v>7.480485600765711</v>
+        <v>-1.490612413236548</v>
       </c>
       <c r="D85">
-        <v>36.97223090285594</v>
+        <v>28.42428644671019</v>
       </c>
       <c r="E85">
-        <v>31.90638951643935</v>
+        <v>32.32954307429586</v>
       </c>
       <c r="F85">
-        <v>35.12174530209023</v>
+        <v>35.54489885994674</v>
       </c>
       <c r="G85">
         <v>5.63</v>
@@ -8257,45 +8257,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M85">
-        <v>3.160957077188121</v>
+        <v>5.217991152640182</v>
       </c>
       <c r="N85">
-        <v>1.58804292281188</v>
+        <v>-0.4689911526401813</v>
       </c>
       <c r="O85">
-        <v>0.5558150229841577</v>
+        <v>-0.1641469034240635</v>
       </c>
       <c r="P85">
-        <v>1.032227899827722</v>
+        <v>-0.3048442492161179</v>
       </c>
       <c r="Q85">
-        <v>3.812227899827722</v>
+        <v>2.475155750783882</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2326196730873658</v>
+        <v>0.2507094922644763</v>
       </c>
       <c r="T85">
-        <v>3.421667920954335</v>
+        <v>3.752989312065201</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.35</v>
+        <v>0.318542126917749</v>
       </c>
       <c r="W85">
-        <v>0.0585</v>
+        <v>0.1000380157684745</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.502393067679536</v>
+        <v>0.91012036262214</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1241454520078347</v>
+        <v>0.1251554520078347</v>
       </c>
       <c r="C86">
-        <v>-1.490612413236533</v>
+        <v>-2.09672179458763</v>
       </c>
       <c r="D86">
-        <v>28.4242864467102</v>
+        <v>28.24133062321562</v>
       </c>
       <c r="E86">
-        <v>32.32954307429586</v>
+        <v>32.75269663215237</v>
       </c>
       <c r="F86">
-        <v>35.54489885994673</v>
+        <v>35.96805241780325</v>
       </c>
       <c r="G86">
         <v>5.63</v>
@@ -8339,37 +8339,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M86">
-        <v>5.217991152640181</v>
+        <v>5.280110094933518</v>
       </c>
       <c r="N86">
-        <v>-0.4689911526401804</v>
+        <v>-0.531110094933517</v>
       </c>
       <c r="O86">
-        <v>-0.1641469034240631</v>
+        <v>-0.1858885332267309</v>
       </c>
       <c r="P86">
-        <v>-0.3048442492161173</v>
+        <v>-0.3452215617067861</v>
       </c>
       <c r="Q86">
-        <v>2.475155750783883</v>
+        <v>2.434778438293214</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2507094922644761</v>
+        <v>0.2643701250821079</v>
       </c>
       <c r="T86">
-        <v>3.752989312065198</v>
+        <v>4.003188599536212</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.318542126917749</v>
+        <v>0.3147945724834225</v>
       </c>
       <c r="W86">
-        <v>0.1000380157684744</v>
+        <v>0.1005881567594336</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9101203626221401</v>
+        <v>0.8994130642383501</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1251554520078347</v>
+        <v>0.1261654520078347</v>
       </c>
       <c r="C87">
-        <v>-2.09672179458763</v>
+        <v>-2.700491010952916</v>
       </c>
       <c r="D87">
-        <v>28.24133062321562</v>
+        <v>28.06071496470684</v>
       </c>
       <c r="E87">
-        <v>32.75269663215237</v>
+        <v>33.17585019000888</v>
       </c>
       <c r="F87">
-        <v>35.96805241780325</v>
+        <v>36.39120597565976</v>
       </c>
       <c r="G87">
         <v>5.63</v>
@@ -8421,37 +8421,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M87">
-        <v>5.280110094933518</v>
+        <v>5.342229037226853</v>
       </c>
       <c r="N87">
-        <v>-0.531110094933517</v>
+        <v>-0.5932290372268527</v>
       </c>
       <c r="O87">
-        <v>-0.1858885332267309</v>
+        <v>-0.2076301630293984</v>
       </c>
       <c r="P87">
-        <v>-0.3452215617067861</v>
+        <v>-0.3855988741974543</v>
       </c>
       <c r="Q87">
-        <v>2.434778438293214</v>
+        <v>2.394401125802545</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2643701250821079</v>
+        <v>0.279982276873687</v>
       </c>
       <c r="T87">
-        <v>4.003188599536212</v>
+        <v>4.289130642360228</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.3147945724834225</v>
+        <v>0.3111341704778013</v>
       </c>
       <c r="W87">
-        <v>0.1005881567594336</v>
+        <v>0.1011255037738588</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8994130642383501</v>
+        <v>0.888954772793718</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1261654520078347</v>
+        <v>0.1271754520078347</v>
       </c>
       <c r="C88">
-        <v>-2.700491010952916</v>
+        <v>-3.301964676142681</v>
       </c>
       <c r="D88">
-        <v>28.06071496470684</v>
+        <v>27.88239485737358</v>
       </c>
       <c r="E88">
-        <v>33.17585019000888</v>
+        <v>33.59900374786539</v>
       </c>
       <c r="F88">
-        <v>36.39120597565976</v>
+        <v>36.81435953351627</v>
       </c>
       <c r="G88">
         <v>5.63</v>
@@ -8503,37 +8503,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M88">
-        <v>5.342229037226853</v>
+        <v>5.404347979520189</v>
       </c>
       <c r="N88">
-        <v>-0.5932290372268527</v>
+        <v>-0.6553479795201884</v>
       </c>
       <c r="O88">
-        <v>-0.2076301630293984</v>
+        <v>-0.2293717928320659</v>
       </c>
       <c r="P88">
-        <v>-0.3855988741974543</v>
+        <v>-0.4259761866881225</v>
       </c>
       <c r="Q88">
-        <v>2.394401125802545</v>
+        <v>2.354023813311877</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.279982276873687</v>
+        <v>0.297996298171663</v>
       </c>
       <c r="T88">
-        <v>4.289130642360228</v>
+        <v>4.61906376869563</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.3111341704778013</v>
+        <v>0.3075579156447231</v>
       </c>
       <c r="W88">
-        <v>0.1011255037738588</v>
+        <v>0.1016504979833547</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.888954772793718</v>
+        <v>0.8787369018420661</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1271754520078347</v>
+        <v>0.1281854520078347</v>
       </c>
       <c r="C89">
-        <v>-3.301964676142681</v>
+        <v>-3.901186277081798</v>
       </c>
       <c r="D89">
-        <v>27.88239485737358</v>
+        <v>27.70632681429097</v>
       </c>
       <c r="E89">
-        <v>33.59900374786539</v>
+        <v>34.0221573057219</v>
       </c>
       <c r="F89">
-        <v>36.81435953351627</v>
+        <v>37.23751309137278</v>
       </c>
       <c r="G89">
         <v>5.63</v>
@@ -8585,37 +8585,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M89">
-        <v>5.404347979520189</v>
+        <v>5.466466921813524</v>
       </c>
       <c r="N89">
-        <v>-0.6553479795201884</v>
+        <v>-0.7174669218135232</v>
       </c>
       <c r="O89">
-        <v>-0.2293717928320659</v>
+        <v>-0.2511134226347331</v>
       </c>
       <c r="P89">
-        <v>-0.4259761866881225</v>
+        <v>-0.4663534991787901</v>
       </c>
       <c r="Q89">
-        <v>2.354023813311877</v>
+        <v>2.31364650082121</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.297996298171663</v>
+        <v>0.3190126563526349</v>
       </c>
       <c r="T89">
-        <v>4.61906376869563</v>
+        <v>5.003985749420266</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.3075579156447231</v>
+        <v>0.3040629393305786</v>
       </c>
       <c r="W89">
-        <v>0.1016504979833547</v>
+        <v>0.1021635605062711</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8787369018420661</v>
+        <v>0.8687512552302246</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1281854520078347</v>
+        <v>0.1291954520078347</v>
       </c>
       <c r="C90">
-        <v>-3.901186277081798</v>
+        <v>-4.498198209165942</v>
       </c>
       <c r="D90">
-        <v>27.70632681429097</v>
+        <v>27.53246844006334</v>
       </c>
       <c r="E90">
-        <v>34.0221573057219</v>
+        <v>34.44531086357841</v>
       </c>
       <c r="F90">
-        <v>37.23751309137278</v>
+        <v>37.66066664922928</v>
       </c>
       <c r="G90">
         <v>5.63</v>
@@ -8667,37 +8667,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M90">
-        <v>5.466466921813524</v>
+        <v>5.528585864106859</v>
       </c>
       <c r="N90">
-        <v>-0.7174669218135232</v>
+        <v>-0.7795858641068589</v>
       </c>
       <c r="O90">
-        <v>-0.2511134226347331</v>
+        <v>-0.2728550524374006</v>
       </c>
       <c r="P90">
-        <v>-0.4663534991787901</v>
+        <v>-0.5067308116694583</v>
       </c>
       <c r="Q90">
-        <v>2.31364650082121</v>
+        <v>2.273269188330541</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3190126563526349</v>
+        <v>0.3438501705665108</v>
       </c>
       <c r="T90">
-        <v>5.003985749420266</v>
+        <v>5.458893544822109</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.3040629393305786</v>
+        <v>0.3006465018100103</v>
       </c>
       <c r="W90">
-        <v>0.1021635605062711</v>
+        <v>0.1026650935342905</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8687512552302246</v>
+        <v>0.858990005171458</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1291954520078347</v>
+        <v>0.1302054520078347</v>
       </c>
       <c r="C91">
-        <v>-4.498198209165942</v>
+        <v>-5.093041810294977</v>
       </c>
       <c r="D91">
-        <v>27.53246844006334</v>
+        <v>27.36077839679081</v>
       </c>
       <c r="E91">
-        <v>34.44531086357841</v>
+        <v>34.86846442143491</v>
       </c>
       <c r="F91">
-        <v>37.66066664922928</v>
+        <v>38.08382020708579</v>
       </c>
       <c r="G91">
         <v>5.63</v>
@@ -8749,37 +8749,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M91">
-        <v>5.528585864106859</v>
+        <v>5.590704806400195</v>
       </c>
       <c r="N91">
-        <v>-0.7795858641068589</v>
+        <v>-0.8417048064001946</v>
       </c>
       <c r="O91">
-        <v>-0.2728550524374006</v>
+        <v>-0.2945966822400681</v>
       </c>
       <c r="P91">
-        <v>-0.5067308116694583</v>
+        <v>-0.5471081241601266</v>
       </c>
       <c r="Q91">
-        <v>2.273269188330541</v>
+        <v>2.232891875839873</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3438501705665108</v>
+        <v>0.3736551876231619</v>
       </c>
       <c r="T91">
-        <v>5.458893544822109</v>
+        <v>6.00478289930432</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.3006465018100103</v>
+        <v>0.2973059851232324</v>
       </c>
       <c r="W91">
-        <v>0.1026650935342905</v>
+        <v>0.1031554813839095</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.858990005171458</v>
+        <v>0.849445671780664</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1302054520078347</v>
+        <v>0.1312154520078347</v>
       </c>
       <c r="C92">
-        <v>-5.093041810294977</v>
+        <v>-5.685757393640934</v>
       </c>
       <c r="D92">
-        <v>27.36077839679081</v>
+        <v>27.19121637130137</v>
       </c>
       <c r="E92">
-        <v>34.86846442143491</v>
+        <v>35.29161797929142</v>
       </c>
       <c r="F92">
-        <v>38.08382020708579</v>
+        <v>38.5069737649423</v>
       </c>
       <c r="G92">
         <v>5.63</v>
@@ -8831,37 +8831,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M92">
-        <v>5.590704806400195</v>
+        <v>5.652823748693531</v>
       </c>
       <c r="N92">
-        <v>-0.8417048064001946</v>
+        <v>-0.9038237486935303</v>
       </c>
       <c r="O92">
-        <v>-0.2945966822400681</v>
+        <v>-0.3163383120427356</v>
       </c>
       <c r="P92">
-        <v>-0.5471081241601266</v>
+        <v>-0.5874854366507947</v>
       </c>
       <c r="Q92">
-        <v>2.232891875839873</v>
+        <v>2.192514563349205</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3736551876231619</v>
+        <v>0.4100835418035133</v>
       </c>
       <c r="T92">
-        <v>6.00478289930432</v>
+        <v>6.671980999227023</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2973059851232324</v>
+        <v>0.2940388863856144</v>
       </c>
       <c r="W92">
-        <v>0.1031554813839095</v>
+        <v>0.1036350914785918</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.849445671780664</v>
+        <v>0.8401111039588984</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1312154520078347</v>
+        <v>0.1322254520078348</v>
       </c>
       <c r="C93">
-        <v>-5.685757393640934</v>
+        <v>-6.276384279204947</v>
       </c>
       <c r="D93">
-        <v>27.19121637130137</v>
+        <v>27.02374304359386</v>
       </c>
       <c r="E93">
-        <v>35.29161797929142</v>
+        <v>35.71477153714793</v>
       </c>
       <c r="F93">
-        <v>38.5069737649423</v>
+        <v>38.93012732279881</v>
       </c>
       <c r="G93">
         <v>5.63</v>
@@ -8913,37 +8913,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M93">
-        <v>5.652823748693531</v>
+        <v>5.714942690986866</v>
       </c>
       <c r="N93">
-        <v>-0.9038237486935303</v>
+        <v>-0.9659426909868651</v>
       </c>
       <c r="O93">
-        <v>-0.3163383120427356</v>
+        <v>-0.3380799418454028</v>
       </c>
       <c r="P93">
-        <v>-0.5874854366507947</v>
+        <v>-0.6278627491414623</v>
       </c>
       <c r="Q93">
-        <v>2.192514563349205</v>
+        <v>2.152137250858537</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4100835418035133</v>
+        <v>0.4556189845289526</v>
       </c>
       <c r="T93">
-        <v>6.671980999227023</v>
+        <v>7.505978624130404</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2940388863856144</v>
+        <v>0.2908428115335969</v>
       </c>
       <c r="W93">
-        <v>0.1036350914785918</v>
+        <v>0.104104275266868</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8401111039588984</v>
+        <v>0.8309794615245626</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1322254520078348</v>
+        <v>0.1332354520078348</v>
       </c>
       <c r="C94">
-        <v>-6.276384279204947</v>
+        <v>-6.864960824215231</v>
       </c>
       <c r="D94">
-        <v>27.02374304359386</v>
+        <v>26.85832005644009</v>
       </c>
       <c r="E94">
-        <v>35.71477153714793</v>
+        <v>36.13792509500444</v>
       </c>
       <c r="F94">
-        <v>38.93012732279881</v>
+        <v>39.35328088065532</v>
       </c>
       <c r="G94">
         <v>5.63</v>
@@ -8995,37 +8995,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M94">
-        <v>5.714942690986866</v>
+        <v>5.777061633280201</v>
       </c>
       <c r="N94">
-        <v>-0.9659426909868651</v>
+        <v>-1.028061633280201</v>
       </c>
       <c r="O94">
-        <v>-0.3380799418454028</v>
+        <v>-0.3598215716480703</v>
       </c>
       <c r="P94">
-        <v>-0.6278627491414623</v>
+        <v>-0.6682400616321306</v>
       </c>
       <c r="Q94">
-        <v>2.152137250858537</v>
+        <v>2.111759938367869</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4556189845289526</v>
+        <v>0.5141645537473745</v>
       </c>
       <c r="T94">
-        <v>7.505978624130404</v>
+        <v>8.578261284720464</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2908428115335969</v>
+        <v>0.2877154694740958</v>
       </c>
       <c r="W94">
-        <v>0.104104275266868</v>
+        <v>0.1045633690812028</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8309794615245626</v>
+        <v>0.8220441984974167</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1332354520078348</v>
+        <v>0.1342454520078347</v>
       </c>
       <c r="C95">
-        <v>-6.864960824215231</v>
+        <v>-7.451524452415342</v>
       </c>
       <c r="D95">
-        <v>26.85832005644009</v>
+        <v>26.69490998609649</v>
       </c>
       <c r="E95">
-        <v>36.13792509500444</v>
+        <v>36.56107865286095</v>
       </c>
       <c r="F95">
-        <v>39.35328088065532</v>
+        <v>39.77643443851183</v>
       </c>
       <c r="G95">
         <v>5.63</v>
@@ -9077,37 +9077,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M95">
-        <v>5.777061633280201</v>
+        <v>5.839180575573537</v>
       </c>
       <c r="N95">
-        <v>-1.028061633280201</v>
+        <v>-1.090180575573537</v>
       </c>
       <c r="O95">
-        <v>-0.3598215716480703</v>
+        <v>-0.3815632014507377</v>
       </c>
       <c r="P95">
-        <v>-0.6682400616321306</v>
+        <v>-0.7086173741227988</v>
       </c>
       <c r="Q95">
-        <v>2.111759938367869</v>
+        <v>2.071382625877201</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5141645537473745</v>
+        <v>0.5922253127052701</v>
       </c>
       <c r="T95">
-        <v>8.578261284720464</v>
+        <v>10.00797149884054</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2877154694740958</v>
+        <v>0.2846546666073501</v>
       </c>
       <c r="W95">
-        <v>0.1045633690812028</v>
+        <v>0.105012694942041</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8220441984974167</v>
+        <v>0.8132990474495718</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1342454520078347</v>
+        <v>0.1352554520078347</v>
       </c>
       <c r="C96">
-        <v>-7.451524452415342</v>
+        <v>-8.036111682289778</v>
       </c>
       <c r="D96">
-        <v>26.69490998609649</v>
+        <v>26.53347631407856</v>
       </c>
       <c r="E96">
-        <v>36.56107865286095</v>
+        <v>36.98423221071746</v>
       </c>
       <c r="F96">
-        <v>39.77643443851183</v>
+        <v>40.19958799636834</v>
       </c>
       <c r="G96">
         <v>5.63</v>
@@ -9159,37 +9159,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M96">
-        <v>5.839180575573537</v>
+        <v>5.901299517866873</v>
       </c>
       <c r="N96">
-        <v>-1.090180575573537</v>
+        <v>-1.152299517866872</v>
       </c>
       <c r="O96">
-        <v>-0.3815632014507377</v>
+        <v>-0.4033048312534053</v>
       </c>
       <c r="P96">
-        <v>-0.7086173741227988</v>
+        <v>-0.7489946866134669</v>
       </c>
       <c r="Q96">
-        <v>2.071382625877201</v>
+        <v>2.031005313386533</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5922253127052701</v>
+        <v>0.7015103752463246</v>
       </c>
       <c r="T96">
-        <v>10.00797149884054</v>
+        <v>12.00956579860866</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2846546666073501</v>
+        <v>0.2816583016956938</v>
       </c>
       <c r="W96">
-        <v>0.105012694942041</v>
+        <v>0.1054525613110722</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8132990474495718</v>
+        <v>0.8047380048448395</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1352554520078347</v>
+        <v>0.1913264862542275</v>
       </c>
       <c r="C97">
-        <v>-8.036111682289778</v>
+        <v>-15.12825673992635</v>
       </c>
       <c r="D97">
-        <v>26.53347631407856</v>
+        <v>19.8644848142985</v>
       </c>
       <c r="E97">
-        <v>36.98423221071746</v>
+        <v>37.40738576857397</v>
       </c>
       <c r="F97">
-        <v>40.19958799636834</v>
+        <v>40.62274155422485</v>
       </c>
       <c r="G97">
         <v>5.63</v>
@@ -9241,45 +9241,45 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M97">
-        <v>5.901299517866873</v>
+        <v>8.157046504088349</v>
       </c>
       <c r="N97">
-        <v>-1.152299517866872</v>
+        <v>-3.408046504088349</v>
       </c>
       <c r="O97">
-        <v>-0.4033048312534053</v>
+        <v>-1.192816276430922</v>
       </c>
       <c r="P97">
-        <v>-0.7489946866134669</v>
+        <v>-2.215230227657427</v>
       </c>
       <c r="Q97">
-        <v>2.031005313386533</v>
+        <v>0.5647697723425731</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7015103752463246</v>
+        <v>0.9459638252177272</v>
       </c>
       <c r="T97">
-        <v>12.00956579860866</v>
+        <v>16.48681658334054</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.2816583016956938</v>
+        <v>0.203768606586578</v>
       </c>
       <c r="W97">
-        <v>0.1054525613110722</v>
+        <v>0.1598832637974151</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8047380048448395</v>
+        <v>0.5821960188187942</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1913264862542275</v>
+        <v>0.1928764862542275</v>
       </c>
       <c r="C98">
-        <v>-15.12825673992635</v>
+        <v>-15.68847619363628</v>
       </c>
       <c r="D98">
-        <v>19.8644848142985</v>
+        <v>19.72741891844507</v>
       </c>
       <c r="E98">
-        <v>37.40738576857397</v>
+        <v>37.83053932643048</v>
       </c>
       <c r="F98">
-        <v>40.62274155422485</v>
+        <v>41.04589511208135</v>
       </c>
       <c r="G98">
         <v>5.63</v>
@@ -9323,37 +9323,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M98">
-        <v>8.157046504088349</v>
+        <v>8.242015738505936</v>
       </c>
       <c r="N98">
-        <v>-3.408046504088349</v>
+        <v>-3.493015738505935</v>
       </c>
       <c r="O98">
-        <v>-1.192816276430922</v>
+        <v>-1.222555508477077</v>
       </c>
       <c r="P98">
-        <v>-2.215230227657427</v>
+        <v>-2.270460230028858</v>
       </c>
       <c r="Q98">
-        <v>0.5647697723425731</v>
+        <v>0.5095397699711417</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9459638252177248</v>
+        <v>1.246018433623633</v>
       </c>
       <c r="T98">
-        <v>16.4868165833405</v>
+        <v>21.98242211112067</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.203768606586578</v>
+        <v>0.2016678993021803</v>
       </c>
       <c r="W98">
-        <v>0.1598832637974151</v>
+        <v>0.1603050858201222</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5821960188187942</v>
+        <v>0.5761939980062294</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1928764862542275</v>
+        <v>0.1944264862542276</v>
       </c>
       <c r="C99">
-        <v>-15.68847619363628</v>
+        <v>-16.24681708702073</v>
       </c>
       <c r="D99">
-        <v>19.72741891844507</v>
+        <v>19.59223158291714</v>
       </c>
       <c r="E99">
-        <v>37.83053932643048</v>
+        <v>38.25369288428698</v>
       </c>
       <c r="F99">
-        <v>41.04589511208135</v>
+        <v>41.46904866993786</v>
       </c>
       <c r="G99">
         <v>5.63</v>
@@ -9405,37 +9405,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M99">
-        <v>8.242015738505936</v>
+        <v>8.326984972923523</v>
       </c>
       <c r="N99">
-        <v>-3.493015738505935</v>
+        <v>-3.577984972923522</v>
       </c>
       <c r="O99">
-        <v>-1.222555508477077</v>
+        <v>-1.252294740523233</v>
       </c>
       <c r="P99">
-        <v>-2.270460230028858</v>
+        <v>-2.325690232400289</v>
       </c>
       <c r="Q99">
-        <v>0.5095397699711417</v>
+        <v>0.4543097675997103</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.246018433623633</v>
+        <v>1.84612765043545</v>
       </c>
       <c r="T99">
-        <v>21.98242211112067</v>
+        <v>32.973633166681</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2016678993021803</v>
+        <v>0.1996100635950152</v>
       </c>
       <c r="W99">
-        <v>0.1603050858201222</v>
+        <v>0.160718299230121</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5761939980062294</v>
+        <v>0.5703144674143291</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1944264862542276</v>
+        <v>0.1959764862542276</v>
       </c>
       <c r="C100">
-        <v>-16.24681708702073</v>
+        <v>-16.80331777721598</v>
       </c>
       <c r="D100">
-        <v>19.59223158291714</v>
+        <v>19.45888445057839</v>
       </c>
       <c r="E100">
-        <v>38.25369288428698</v>
+        <v>38.67684644214349</v>
       </c>
       <c r="F100">
-        <v>41.46904866993786</v>
+        <v>41.89220222779437</v>
       </c>
       <c r="G100">
         <v>5.63</v>
@@ -9487,37 +9487,37 @@
         <v>4.749000000000001</v>
       </c>
       <c r="M100">
-        <v>8.326984972923523</v>
+        <v>8.411954207341109</v>
       </c>
       <c r="N100">
-        <v>-3.577984972923522</v>
+        <v>-3.662954207341109</v>
       </c>
       <c r="O100">
-        <v>-1.252294740523233</v>
+        <v>-1.282033972569388</v>
       </c>
       <c r="P100">
-        <v>-2.325690232400289</v>
+        <v>-2.380920234771721</v>
       </c>
       <c r="Q100">
-        <v>0.4543097675997103</v>
+        <v>0.3990797652282789</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.84612765043545</v>
+        <v>3.6464553008709</v>
       </c>
       <c r="T100">
-        <v>32.973633166681</v>
+        <v>65.94726633336202</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1996100635950152</v>
+        <v>0.1975938003263787</v>
       </c>
       <c r="W100">
-        <v>0.160718299230121</v>
+        <v>0.1611231648944632</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5703144674143291</v>
+        <v>0.5645537152182247</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1959764862542276</v>
-      </c>
-      <c r="C101">
-        <v>-16.80331777721598</v>
-      </c>
-      <c r="D101">
-        <v>19.45888445057839</v>
-      </c>
-      <c r="E101">
-        <v>38.67684644214349</v>
-      </c>
-      <c r="F101">
-        <v>41.89220222779437</v>
-      </c>
-      <c r="G101">
-        <v>5.63</v>
-      </c>
-      <c r="H101">
-        <v>39.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.529</v>
-      </c>
-      <c r="K101">
-        <v>2.78</v>
-      </c>
-      <c r="L101">
-        <v>4.749000000000001</v>
-      </c>
-      <c r="M101">
-        <v>8.411954207341109</v>
-      </c>
-      <c r="N101">
-        <v>-3.662954207341109</v>
-      </c>
-      <c r="O101">
-        <v>-1.282033972569388</v>
-      </c>
-      <c r="P101">
-        <v>-2.380920234771721</v>
-      </c>
-      <c r="Q101">
-        <v>0.3990797652282789</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.6464553008709</v>
-      </c>
-      <c r="T101">
-        <v>65.94726633336202</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1975938003263787</v>
-      </c>
-      <c r="W101">
-        <v>0.1611231648944632</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5645537152182247</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
